--- a/assets/[Multi-table]_SDGym_Runs.xlsx
+++ b/assets/[Multi-table]_SDGym_Runs.xlsx
@@ -8,10 +8,12 @@
   </bookViews>
   <sheets>
     <sheet name="Wins" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2026-02-01_Detailed_results" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="2026-02-01_plot_data" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="2025-12-23_Detailed_results" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="2025-12-23_plot_data" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="2026-03-01_Detailed_results" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2026-03-01_plot_data" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="2026-02-01_Detailed_results" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="2026-02-01_plot_data" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="2025-12-23_Detailed_results" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="2025-12-23_plot_data" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,12 +431,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="53" customWidth="1" min="2" max="2"/>
-    <col width="57" customWidth="1" min="3" max="3"/>
+    <col width="53" customWidth="1" min="3" max="3"/>
+    <col width="57" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -445,10 +448,15 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>03_01_2026 - # datasets: 54 - sdgym version: 0.13.1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>02_01_2026 - # datasets: 54 - sdgym version: 0.13.0</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>12_23_2025 - # datasets: 7 - sdgym version: 0.12.2.dev0</t>
         </is>
@@ -464,6 +472,9 @@
         <v>8</v>
       </c>
       <c r="C2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -474,9 +485,12 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>40</v>
+      </c>
+      <c r="C3" t="n">
         <v>38</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>3</v>
       </c>
     </row>
@@ -487,9 +501,12 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
         <v>2</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -499,6 +516,9838 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N217"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="267" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="5" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Synthesizer</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Dataset_Size_MB</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Train_Time</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Peak_Memory_MB</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Synthesizer_Size_MB</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Sample_Time</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Evaluate_Time</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Diagnostic_Score</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Quality_Score</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Adjusted_Total_Time</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Adjusted_Quality_Score</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Accidents</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Synthesizer Timeout</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>345857.04862</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.3103486662372166</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Accidents</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>219.334096</v>
+      </c>
+      <c r="D3" t="n">
+        <v>358.709781</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2163.814255</v>
+      </c>
+      <c r="F3" t="n">
+        <v>43.037512</v>
+      </c>
+      <c r="G3" t="n">
+        <v>54.19535</v>
+      </c>
+      <c r="H3" t="n">
+        <v>827.943703</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.5954709920794259</v>
+      </c>
+      <c r="L3" t="n">
+        <v>419.2464230000001</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.5954709920794259</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Accidents</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>219.334096</v>
+      </c>
+      <c r="D4" t="n">
+        <v>318.87942</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1892.096014</v>
+      </c>
+      <c r="F4" t="n">
+        <v>28.878202</v>
+      </c>
+      <c r="G4" t="n">
+        <v>59.656363</v>
+      </c>
+      <c r="H4" t="n">
+        <v>830.1832529999999</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.592826439841007</v>
+      </c>
+      <c r="L4" t="n">
+        <v>384.877075</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.592826439841007</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Accidents</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>219.334096</v>
+      </c>
+      <c r="D5" t="n">
+        <v>195.866862</v>
+      </c>
+      <c r="E5" t="n">
+        <v>8797.761489</v>
+      </c>
+      <c r="F5" t="n">
+        <v>175.807822</v>
+      </c>
+      <c r="G5" t="n">
+        <v>61.181758</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3052.045677</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.9170220114299984</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.3103486662372166</v>
+      </c>
+      <c r="L5" t="n">
+        <v>452.915482</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.3103486662372166</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Atherosclerosis</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>6.62428</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3032.589503</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2798.88743</v>
+      </c>
+      <c r="F6" t="n">
+        <v>206.895092</v>
+      </c>
+      <c r="G6" t="n">
+        <v>6982.603523</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1661.081394</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.7412491277081574</v>
+      </c>
+      <c r="L6" t="n">
+        <v>10061.765082</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.7412491277081574</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Atherosclerosis</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>6.62428</v>
+      </c>
+      <c r="D7" t="n">
+        <v>16.342397</v>
+      </c>
+      <c r="E7" t="n">
+        <v>88.627107</v>
+      </c>
+      <c r="F7" t="n">
+        <v>4.227103</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3.982848</v>
+      </c>
+      <c r="H7" t="n">
+        <v>56.236949</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.7733684836818895</v>
+      </c>
+      <c r="L7" t="n">
+        <v>26.543476</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.7733684836818895</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Atherosclerosis</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>6.62428</v>
+      </c>
+      <c r="D8" t="n">
+        <v>14.299732</v>
+      </c>
+      <c r="E8" t="n">
+        <v>80.08163500000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3.817209</v>
+      </c>
+      <c r="G8" t="n">
+        <v>5.073694</v>
+      </c>
+      <c r="H8" t="n">
+        <v>56.681877</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.7650116192280561</v>
+      </c>
+      <c r="L8" t="n">
+        <v>25.591657</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.7650116192280561</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Atherosclerosis</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>6.62428</v>
+      </c>
+      <c r="D9" t="n">
+        <v>46.572056</v>
+      </c>
+      <c r="E9" t="n">
+        <v>300.261543</v>
+      </c>
+      <c r="F9" t="n">
+        <v>8.205313</v>
+      </c>
+      <c r="G9" t="n">
+        <v>19.197986</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1513.810385</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.8447861687131438</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.5671369830795265</v>
+      </c>
+      <c r="L9" t="n">
+        <v>112.342098</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.5671369830795265</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>AustralianFootball</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Out of Memory Error</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>0.785349</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.4225208651670076</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>AustralianFootball</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>31.178128</v>
+      </c>
+      <c r="D11" t="n">
+        <v>27.670705</v>
+      </c>
+      <c r="E11" t="n">
+        <v>418.149701</v>
+      </c>
+      <c r="F11" t="n">
+        <v>7.910662</v>
+      </c>
+      <c r="G11" t="n">
+        <v>6.139387</v>
+      </c>
+      <c r="H11" t="n">
+        <v>26.05591</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.6918659197256948</v>
+      </c>
+      <c r="L11" t="n">
+        <v>34.595441</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.6918659197256948</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>AustralianFootball</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>31.178128</v>
+      </c>
+      <c r="D12" t="n">
+        <v>19.831916</v>
+      </c>
+      <c r="E12" t="n">
+        <v>344.620765</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.967222</v>
+      </c>
+      <c r="G12" t="n">
+        <v>9.143336</v>
+      </c>
+      <c r="H12" t="n">
+        <v>25.741452</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.6735098963155296</v>
+      </c>
+      <c r="L12" t="n">
+        <v>29.760601</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.6735098963155296</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>AustralianFootball</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>31.178128</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.785349</v>
+      </c>
+      <c r="E13" t="n">
+        <v>157.084175</v>
+      </c>
+      <c r="F13" t="n">
+        <v>32.785873</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.296175</v>
+      </c>
+      <c r="H13" t="n">
+        <v>25.486388</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.904524119162164</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.4225208651670076</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.866873</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.4225208651670076</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Biodegradability</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.567784</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1145.279296</v>
+      </c>
+      <c r="E14" t="n">
+        <v>732.783775</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3.015925</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2912.484431</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.270713</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.7860000761699991</v>
+      </c>
+      <c r="L14" t="n">
+        <v>4057.923804</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.7860000761699991</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Biodegradability</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0.567784</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3.265769</v>
+      </c>
+      <c r="E15" t="n">
+        <v>25.292748</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.784188</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.836412</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.261667</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.7490832250910372</v>
+      </c>
+      <c r="L15" t="n">
+        <v>4.29287</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.7490832250910372</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Biodegradability</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.567784</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.26032</v>
+      </c>
+      <c r="E16" t="n">
+        <v>23.495478</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.886127</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.606555</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.261037</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.7282431463850354</v>
+      </c>
+      <c r="L16" t="n">
+        <v>3.057564</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.7282431463850354</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Biodegradability</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.567784</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.160077</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4.542338</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.908922</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.053578</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.252832</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.8758458853770623</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.5078768132981422</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.373732</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.5078768132981422</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Bupa</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.042584</v>
+      </c>
+      <c r="D18" t="n">
+        <v>227.955284</v>
+      </c>
+      <c r="E18" t="n">
+        <v>32.413835</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3.297055</v>
+      </c>
+      <c r="G18" t="n">
+        <v>285.621409</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.180729</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.8715450310559006</v>
+      </c>
+      <c r="L18" t="n">
+        <v>513.698828</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.8715450310559006</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Bupa</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.042584</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3.904447</v>
+      </c>
+      <c r="E19" t="n">
+        <v>34.602804</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3.392856</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.62424</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.190948</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.8674042443064183</v>
+      </c>
+      <c r="L19" t="n">
+        <v>4.670111</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.8674042443064183</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Bupa</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.042584</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.850555</v>
+      </c>
+      <c r="E20" t="n">
+        <v>29.410392</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.973878</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.313668</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.1875279999999999</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.8692675983436853</v>
+      </c>
+      <c r="L20" t="n">
+        <v>3.305647</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.8692675983436853</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Bupa</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.042584</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.122135</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.442706</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.058378</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.030067</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.179035</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.807199409554482</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.5507116977225672</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.274337</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.5507116977225672</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CORA</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1.792352</v>
+      </c>
+      <c r="D22" t="n">
+        <v>750.239544</v>
+      </c>
+      <c r="E22" t="n">
+        <v>267.858181</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.613795</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1120.498569</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.260999</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.7511962411037322</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1870.821268</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.7511962411037322</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CORA</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1.792352</v>
+      </c>
+      <c r="D23" t="n">
+        <v>5.19441</v>
+      </c>
+      <c r="E23" t="n">
+        <v>27.332701</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3.043006</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1.262455</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.260352</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.8429858381471252</v>
+      </c>
+      <c r="L23" t="n">
+        <v>6.552994000000001</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.8429858381471252</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CORA</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1.792352</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2.236744</v>
+      </c>
+      <c r="E24" t="n">
+        <v>22.085153</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.429834</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.105168</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.265258</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.8194447743932295</v>
+      </c>
+      <c r="L24" t="n">
+        <v>3.438041</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.8194447743932295</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CORA</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1.792352</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.08315500000000001</v>
+      </c>
+      <c r="E25" t="n">
+        <v>8.842390999999999</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.136405</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.026307</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.2503869999999999</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.7451543556426032</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.3038710363656727</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.192617</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.3038710363656727</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Carcinogenesis</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.945536</v>
+      </c>
+      <c r="D26" t="n">
+        <v>105.297169</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1927.542141</v>
+      </c>
+      <c r="F26" t="n">
+        <v>4.034082</v>
+      </c>
+      <c r="G26" t="n">
+        <v>8778.79299</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.485411</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.7838217915233648</v>
+      </c>
+      <c r="L26" t="n">
+        <v>8884.227857</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.7838217915233648</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Carcinogenesis</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.945536</v>
+      </c>
+      <c r="D27" t="n">
+        <v>6.187069</v>
+      </c>
+      <c r="E27" t="n">
+        <v>25.312887</v>
+      </c>
+      <c r="F27" t="n">
+        <v>3.277089</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2.108981</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.474909</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.7796945326845552</v>
+      </c>
+      <c r="L27" t="n">
+        <v>8.464406</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.7796945326845552</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Carcinogenesis</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.945536</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2.685559</v>
+      </c>
+      <c r="E28" t="n">
+        <v>22.50102</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.204302</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.621723</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.467855</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.751691163221671</v>
+      </c>
+      <c r="L28" t="n">
+        <v>4.475638</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.751691163221671</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Carcinogenesis</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.945536</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.137698</v>
+      </c>
+      <c r="E29" t="n">
+        <v>5.201511</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.819595</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.033639</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.47668</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.8703148805907586</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.5143309245982678</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.3090349999999999</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.5143309245982678</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Chess</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.249168</v>
+      </c>
+      <c r="D30" t="n">
+        <v>30.881141</v>
+      </c>
+      <c r="E30" t="n">
+        <v>103.590958</v>
+      </c>
+      <c r="F30" t="n">
+        <v>13.656949</v>
+      </c>
+      <c r="G30" t="n">
+        <v>318.941036</v>
+      </c>
+      <c r="H30" t="n">
+        <v>4.98626</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.5313581091037832</v>
+      </c>
+      <c r="L30" t="n">
+        <v>350.072027</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.5313581091037832</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Chess</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.249168</v>
+      </c>
+      <c r="D31" t="n">
+        <v>3.724235</v>
+      </c>
+      <c r="E31" t="n">
+        <v>17.80924</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.948395</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.828803</v>
+      </c>
+      <c r="H31" t="n">
+        <v>5.038962000000001</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.6273182946582756</v>
+      </c>
+      <c r="L31" t="n">
+        <v>4.810179</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.6273182946582756</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Chess</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.249168</v>
+      </c>
+      <c r="D32" t="n">
+        <v>3.46672</v>
+      </c>
+      <c r="E32" t="n">
+        <v>17.590975</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.845843</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.800356</v>
+      </c>
+      <c r="H32" t="n">
+        <v>5.116101</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.6056028665007028</v>
+      </c>
+      <c r="L32" t="n">
+        <v>4.524217</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.6056028665007028</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Chess</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.249168</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.24985</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1.208011</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.241291</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.054717</v>
+      </c>
+      <c r="H33" t="n">
+        <v>4.952572999999999</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.9286421849147218</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.4174148957958863</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.5544169999999999</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.4174148957958863</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>9.928775999999999</v>
+      </c>
+      <c r="D34" t="n">
+        <v>208.677285</v>
+      </c>
+      <c r="F34" t="n">
+        <v>91.780334</v>
+      </c>
+      <c r="G34" t="n">
+        <v>3.128998</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>TypeError: '&lt;' not supported between instances of 'int' and 'str'</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>215.420483</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.3874713894583317</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>9.928775999999999</v>
+      </c>
+      <c r="D35" t="n">
+        <v>13.510809</v>
+      </c>
+      <c r="E35" t="n">
+        <v>141.391015</v>
+      </c>
+      <c r="F35" t="n">
+        <v>3.25493</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2.550064</v>
+      </c>
+      <c r="H35" t="n">
+        <v>23.211513</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.6329428463639473</v>
+      </c>
+      <c r="L35" t="n">
+        <v>19.384634</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.6329428463639473</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>9.928775999999999</v>
+      </c>
+      <c r="D36" t="n">
+        <v>10.706553</v>
+      </c>
+      <c r="E36" t="n">
+        <v>135.096471</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.3882</v>
+      </c>
+      <c r="G36" t="n">
+        <v>4.560501</v>
+      </c>
+      <c r="H36" t="n">
+        <v>23.117083</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.6303397406615706</v>
+      </c>
+      <c r="L36" t="n">
+        <v>18.590815</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.6303397406615706</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>9.928775999999999</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2.651991</v>
+      </c>
+      <c r="E37" t="n">
+        <v>59.031552</v>
+      </c>
+      <c r="F37" t="n">
+        <v>10.621059</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.962209</v>
+      </c>
+      <c r="H37" t="n">
+        <v>22.719304</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.7961968249923715</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.3874713894583317</v>
+      </c>
+      <c r="L37" t="n">
+        <v>6.266191</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.3874713894583317</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>DCG</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.246432</v>
+      </c>
+      <c r="D38" t="n">
+        <v>133.743437</v>
+      </c>
+      <c r="E38" t="n">
+        <v>26.803372</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.093373</v>
+      </c>
+      <c r="G38" t="n">
+        <v>176.414339</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.080401</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.6624598713012347</v>
+      </c>
+      <c r="L38" t="n">
+        <v>310.20542</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.6624598713012347</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>DCG</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.246432</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1.461641</v>
+      </c>
+      <c r="E39" t="n">
+        <v>11.255535</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.206477</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.306089</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.070338</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.8386510411666098</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1.817225</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.8386510411666098</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>DCG</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.246432</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.841602</v>
+      </c>
+      <c r="E40" t="n">
+        <v>10.093096</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.995671</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.252232</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.07141</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.785721770308791</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1.143329</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.785721770308791</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>DCG</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.246432</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.047644</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1.305038</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.220401</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.009216999999999999</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.075865</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.840489208704548</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.7286028370672749</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.104505</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.7286028370672749</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Dunur</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.01456</v>
+      </c>
+      <c r="D42" t="n">
+        <v>15.61868</v>
+      </c>
+      <c r="E42" t="n">
+        <v>52.312557</v>
+      </c>
+      <c r="F42" t="n">
+        <v>6.206941</v>
+      </c>
+      <c r="G42" t="n">
+        <v>82.608469</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.480738</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.9486359761295824</v>
+      </c>
+      <c r="L42" t="n">
+        <v>98.478979</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.9486359761295824</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Dunur</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.01456</v>
+      </c>
+      <c r="D43" t="n">
+        <v>8.811419000000001</v>
+      </c>
+      <c r="E43" t="n">
+        <v>55.878078</v>
+      </c>
+      <c r="F43" t="n">
+        <v>6.724881</v>
+      </c>
+      <c r="G43" t="n">
+        <v>2.067024</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.547388</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.9792199488491048</v>
+      </c>
+      <c r="L43" t="n">
+        <v>11.143135</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.9792199488491048</v>
+      </c>
+      <c r="N43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Dunur</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.01456</v>
+      </c>
+      <c r="D44" t="n">
+        <v>5.538452</v>
+      </c>
+      <c r="E44" t="n">
+        <v>56.176428</v>
+      </c>
+      <c r="F44" t="n">
+        <v>5.30359</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.612945</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.502363</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.9639013213981245</v>
+      </c>
+      <c r="L44" t="n">
+        <v>6.416089</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.9639013213981245</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Dunur</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.01456</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.25183</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.328352</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.022434</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.056425</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.476728</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.8031711778914463</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.6887734441602729</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.5600849999999999</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.6887734441602729</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Elti</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.041752</v>
+      </c>
+      <c r="D46" t="n">
+        <v>13.754674</v>
+      </c>
+      <c r="E46" t="n">
+        <v>42.417675</v>
+      </c>
+      <c r="F46" t="n">
+        <v>3.958302</v>
+      </c>
+      <c r="G46" t="n">
+        <v>99.211117</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.307515</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.9151942645698428</v>
+      </c>
+      <c r="L46" t="n">
+        <v>113.128839</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.9151942645698428</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Elti</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.041752</v>
+      </c>
+      <c r="D47" t="n">
+        <v>5.048555</v>
+      </c>
+      <c r="E47" t="n">
+        <v>40.083124</v>
+      </c>
+      <c r="F47" t="n">
+        <v>4.452081</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1.401345</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.308108</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.9792553191489362</v>
+      </c>
+      <c r="L47" t="n">
+        <v>6.643577000000001</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.9792553191489362</v>
+      </c>
+      <c r="N47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Elti</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.041752</v>
+      </c>
+      <c r="D48" t="n">
+        <v>3.683847</v>
+      </c>
+      <c r="E48" t="n">
+        <v>37.932704</v>
+      </c>
+      <c r="F48" t="n">
+        <v>3.563813</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.386543</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.3205909999999999</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.9665587419056428</v>
+      </c>
+      <c r="L48" t="n">
+        <v>4.264067</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.9665587419056428</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Elti</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.041752</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.163048</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.412077</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.048915</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.038444</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.30519</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.8221151642811436</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.6832793709528214</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.36454</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.6832793709528214</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>FNHK</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>120.004544</v>
+      </c>
+      <c r="D50" t="n">
+        <v>7744.88486</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1248.151047</v>
+      </c>
+      <c r="F50" t="n">
+        <v>5.215485</v>
+      </c>
+      <c r="G50" t="n">
+        <v>68338.68748199999</v>
+      </c>
+      <c r="H50" t="n">
+        <v>32.509337</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.6221130574247633</v>
+      </c>
+      <c r="L50" t="n">
+        <v>76085.02816999999</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.6221130574247633</v>
+      </c>
+      <c r="N50" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>FNHK</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>120.004544</v>
+      </c>
+      <c r="D51" t="n">
+        <v>116.150688</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1567.79588</v>
+      </c>
+      <c r="F51" t="n">
+        <v>79.959582</v>
+      </c>
+      <c r="G51" t="n">
+        <v>646.292207</v>
+      </c>
+      <c r="H51" t="n">
+        <v>32.126233</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.6073623009018826</v>
+      </c>
+      <c r="L51" t="n">
+        <v>763.9771049999999</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.6073623009018826</v>
+      </c>
+      <c r="N51" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>FNHK</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>120.004544</v>
+      </c>
+      <c r="D52" t="n">
+        <v>73.19919299999999</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1142.145903</v>
+      </c>
+      <c r="F52" t="n">
+        <v>4.509789</v>
+      </c>
+      <c r="G52" t="n">
+        <v>647.722204</v>
+      </c>
+      <c r="H52" t="n">
+        <v>31.964058</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.5580130362124243</v>
+      </c>
+      <c r="L52" t="n">
+        <v>722.455607</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.5580130362124243</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>FNHK</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>120.004544</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1.455828</v>
+      </c>
+      <c r="E53" t="n">
+        <v>532.260162</v>
+      </c>
+      <c r="F53" t="n">
+        <v>152.614554</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1.656503</v>
+      </c>
+      <c r="H53" t="n">
+        <v>29.478401</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.8671590854246435</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.3708493353329065</v>
+      </c>
+      <c r="L53" t="n">
+        <v>4.568159</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.3708493353329065</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>1.382168</v>
+      </c>
+      <c r="D54" t="n">
+        <v>54.088203</v>
+      </c>
+      <c r="E54" t="n">
+        <v>104.664668</v>
+      </c>
+      <c r="F54" t="n">
+        <v>4.484456</v>
+      </c>
+      <c r="G54" t="n">
+        <v>172.749245</v>
+      </c>
+      <c r="H54" t="n">
+        <v>93.92609</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.9641910202618568</v>
+      </c>
+      <c r="L54" t="n">
+        <v>229.308708</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.9641910202618568</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>1.382168</v>
+      </c>
+      <c r="D55" t="n">
+        <v>17.115867</v>
+      </c>
+      <c r="E55" t="n">
+        <v>28.892024</v>
+      </c>
+      <c r="F55" t="n">
+        <v>4.788942</v>
+      </c>
+      <c r="G55" t="n">
+        <v>4.080929</v>
+      </c>
+      <c r="H55" t="n">
+        <v>95.11767</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.9800667904293642</v>
+      </c>
+      <c r="L55" t="n">
+        <v>23.721005</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.9800667904293642</v>
+      </c>
+      <c r="N55" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>1.382168</v>
+      </c>
+      <c r="D56" t="n">
+        <v>16.497568</v>
+      </c>
+      <c r="E56" t="n">
+        <v>24.186439</v>
+      </c>
+      <c r="F56" t="n">
+        <v>4.459575</v>
+      </c>
+      <c r="G56" t="n">
+        <v>3.974399</v>
+      </c>
+      <c r="H56" t="n">
+        <v>94.075671</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.9743477716752392</v>
+      </c>
+      <c r="L56" t="n">
+        <v>22.996176</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.9743477716752392</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>1.382168</v>
+      </c>
+      <c r="D57" t="n">
+        <v>2.47126</v>
+      </c>
+      <c r="E57" t="n">
+        <v>7.534597</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1.435814</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.212751</v>
+      </c>
+      <c r="H57" t="n">
+        <v>93.040964</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.8558986532294749</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.3503221414896294</v>
+      </c>
+      <c r="L57" t="n">
+        <v>5.155271</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.3503221414896294</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Hepatitis_std</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.6778</v>
+      </c>
+      <c r="D58" t="n">
+        <v>17.679879</v>
+      </c>
+      <c r="E58" t="n">
+        <v>539.149602</v>
+      </c>
+      <c r="F58" t="n">
+        <v>2.716432</v>
+      </c>
+      <c r="G58" t="n">
+        <v>978.2325939999999</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.405463</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.8869490994756269</v>
+      </c>
+      <c r="L58" t="n">
+        <v>996.114599</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.8869490994756269</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Hepatitis_std</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.6778</v>
+      </c>
+      <c r="D59" t="n">
+        <v>4.357853</v>
+      </c>
+      <c r="E59" t="n">
+        <v>30.148576</v>
+      </c>
+      <c r="F59" t="n">
+        <v>3.196458</v>
+      </c>
+      <c r="G59" t="n">
+        <v>1.174273</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.413959</v>
+      </c>
+      <c r="I59" t="n">
+        <v>1</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0.9306157325817344</v>
+      </c>
+      <c r="L59" t="n">
+        <v>5.763612</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0.9306157325817344</v>
+      </c>
+      <c r="N59" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Hepatitis_std</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.6778</v>
+      </c>
+      <c r="D60" t="n">
+        <v>3.148844</v>
+      </c>
+      <c r="E60" t="n">
+        <v>28.667817</v>
+      </c>
+      <c r="F60" t="n">
+        <v>2.623137</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.843581</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.413764</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0.929707848413666</v>
+      </c>
+      <c r="L60" t="n">
+        <v>4.223911</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.929707848413666</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Hepatitis_std</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>0.6778</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0.202126</v>
+      </c>
+      <c r="E61" t="n">
+        <v>2.992863</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.695972</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.030729</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.405248</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.8575075365252157</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.7067168462497554</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0.434981</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.7067168462497554</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Mesh</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0.041704</v>
+      </c>
+      <c r="D62" t="n">
+        <v>23.475208</v>
+      </c>
+      <c r="E62" t="n">
+        <v>89.746483</v>
+      </c>
+      <c r="F62" t="n">
+        <v>9.136566999999999</v>
+      </c>
+      <c r="G62" t="n">
+        <v>871.209009</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.572792</v>
+      </c>
+      <c r="I62" t="n">
+        <v>1</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0.8707377454679612</v>
+      </c>
+      <c r="L62" t="n">
+        <v>894.955198</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0.8707377454679612</v>
+      </c>
+      <c r="N62" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Mesh</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0.041704</v>
+      </c>
+      <c r="D63" t="n">
+        <v>11.810013</v>
+      </c>
+      <c r="E63" t="n">
+        <v>87.12357299999999</v>
+      </c>
+      <c r="F63" t="n">
+        <v>10.129975</v>
+      </c>
+      <c r="G63" t="n">
+        <v>2.246478</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.595275</v>
+      </c>
+      <c r="I63" t="n">
+        <v>1</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0.8932361104123694</v>
+      </c>
+      <c r="L63" t="n">
+        <v>14.35663</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0.8932361104123694</v>
+      </c>
+      <c r="N63" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Mesh</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>0.041704</v>
+      </c>
+      <c r="D64" t="n">
+        <v>8.191184</v>
+      </c>
+      <c r="E64" t="n">
+        <v>81.782956</v>
+      </c>
+      <c r="F64" t="n">
+        <v>8.527278000000001</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.611582</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.60053</v>
+      </c>
+      <c r="I64" t="n">
+        <v>1</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0.8668035501668596</v>
+      </c>
+      <c r="L64" t="n">
+        <v>9.102905</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0.8668035501668596</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Mesh</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0.041704</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0.270981</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.496158</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.041333</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.063433</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.565509</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.8356820613237415</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0.7852369153628147</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0.605395</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0.7852369153628147</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Mooney_Family</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>0.113528</v>
+      </c>
+      <c r="D66" t="n">
+        <v>125.72002</v>
+      </c>
+      <c r="E66" t="n">
+        <v>240.363712</v>
+      </c>
+      <c r="F66" t="n">
+        <v>39.199225</v>
+      </c>
+      <c r="G66" t="n">
+        <v>1332.560135</v>
+      </c>
+      <c r="H66" t="n">
+        <v>2.486272</v>
+      </c>
+      <c r="I66" t="n">
+        <v>1</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0.8519748984865265</v>
+      </c>
+      <c r="L66" t="n">
+        <v>1459.518514</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0.8519748984865265</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Mooney_Family</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0.113528</v>
+      </c>
+      <c r="D67" t="n">
+        <v>34.945481</v>
+      </c>
+      <c r="E67" t="n">
+        <v>211.027227</v>
+      </c>
+      <c r="F67" t="n">
+        <v>27.656366</v>
+      </c>
+      <c r="G67" t="n">
+        <v>10.983371</v>
+      </c>
+      <c r="H67" t="n">
+        <v>3.026615</v>
+      </c>
+      <c r="I67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0.9751445797957424</v>
+      </c>
+      <c r="L67" t="n">
+        <v>47.276161</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0.9751445797957424</v>
+      </c>
+      <c r="N67" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Mooney_Family</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>0.113528</v>
+      </c>
+      <c r="D68" t="n">
+        <v>20.618678</v>
+      </c>
+      <c r="E68" t="n">
+        <v>183.669474</v>
+      </c>
+      <c r="F68" t="n">
+        <v>20.18433</v>
+      </c>
+      <c r="G68" t="n">
+        <v>3.431675</v>
+      </c>
+      <c r="H68" t="n">
+        <v>2.664234</v>
+      </c>
+      <c r="I68" t="n">
+        <v>1</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0.9133136458717854</v>
+      </c>
+      <c r="L68" t="n">
+        <v>25.397662</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0.9133136458717854</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Mooney_Family</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>0.113528</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1.238359</v>
+      </c>
+      <c r="E69" t="n">
+        <v>1.402744</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.14144</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.234862</v>
+      </c>
+      <c r="H69" t="n">
+        <v>2.506185</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.7940097897089445</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.8124807232671953</v>
+      </c>
+      <c r="L69" t="n">
+        <v>2.71158</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0.8124807232671953</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>MuskSmall</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>0.641472</v>
+      </c>
+      <c r="D70" t="n">
+        <v>3700.809136</v>
+      </c>
+      <c r="E70" t="n">
+        <v>22829.664389</v>
+      </c>
+      <c r="F70" t="n">
+        <v>1811.190973</v>
+      </c>
+      <c r="G70" t="n">
+        <v>699.580521</v>
+      </c>
+      <c r="H70" t="n">
+        <v>56.119277</v>
+      </c>
+      <c r="I70" t="n">
+        <v>1</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.8046746012420044</v>
+      </c>
+      <c r="L70" t="n">
+        <v>4401.072758</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0.8046746012420044</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>MuskSmall</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>0.641472</v>
+      </c>
+      <c r="D71" t="n">
+        <v>11.28738</v>
+      </c>
+      <c r="E71" t="n">
+        <v>17.486733</v>
+      </c>
+      <c r="F71" t="n">
+        <v>3.158213</v>
+      </c>
+      <c r="G71" t="n">
+        <v>2.488061</v>
+      </c>
+      <c r="H71" t="n">
+        <v>58.854447</v>
+      </c>
+      <c r="I71" t="n">
+        <v>1</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.8754169811433258</v>
+      </c>
+      <c r="L71" t="n">
+        <v>14.532397</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0.8754169811433258</v>
+      </c>
+      <c r="N71" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>MuskSmall</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>0.641472</v>
+      </c>
+      <c r="D72" t="n">
+        <v>11.420157</v>
+      </c>
+      <c r="E72" t="n">
+        <v>17.257678</v>
+      </c>
+      <c r="F72" t="n">
+        <v>3.073892</v>
+      </c>
+      <c r="G72" t="n">
+        <v>2.744418</v>
+      </c>
+      <c r="H72" t="n">
+        <v>60.661456</v>
+      </c>
+      <c r="I72" t="n">
+        <v>1</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.8649409812779444</v>
+      </c>
+      <c r="L72" t="n">
+        <v>14.921531</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0.8649409812779444</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>MuskSmall</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>0.641472</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.683101</v>
+      </c>
+      <c r="E73" t="n">
+        <v>3.919394</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.649772</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.125198</v>
+      </c>
+      <c r="H73" t="n">
+        <v>56.090129</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.9350882493465614</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.6717810973374275</v>
+      </c>
+      <c r="L73" t="n">
+        <v>1.4914</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0.6717810973374275</v>
+      </c>
+      <c r="N73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>NBA</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Out of Memory Error</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>0.183121</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0.5450965996276989</v>
+      </c>
+      <c r="N74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>NBA</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>0.149832</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2.891518</v>
+      </c>
+      <c r="E75" t="n">
+        <v>22.114112</v>
+      </c>
+      <c r="F75" t="n">
+        <v>2.139952</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="H75" t="n">
+        <v>1.254413</v>
+      </c>
+      <c r="I75" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.7050810191811504</v>
+      </c>
+      <c r="L75" t="n">
+        <v>3.765041</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.7050810191811504</v>
+      </c>
+      <c r="N75" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>NBA</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>0.149832</v>
+      </c>
+      <c r="D76" t="n">
+        <v>2.3799</v>
+      </c>
+      <c r="E76" t="n">
+        <v>21.382924</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1.887317</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.519719</v>
+      </c>
+      <c r="H76" t="n">
+        <v>1.266534</v>
+      </c>
+      <c r="I76" t="n">
+        <v>1</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.6952561460706215</v>
+      </c>
+      <c r="L76" t="n">
+        <v>3.08274</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0.6952561460706215</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>NBA</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>0.149832</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0.183121</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.874287</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.158243</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.030314</v>
+      </c>
+      <c r="H77" t="n">
+        <v>1.259442</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.8950079110616121</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.5450965996276989</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0.396556</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0.5450965996276989</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>NCAA</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Synthesizer Timeout</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>345605.9030779999</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0.5164218840632655</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>NCAA</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>27.152528</v>
+      </c>
+      <c r="D79" t="n">
+        <v>33.325829</v>
+      </c>
+      <c r="E79" t="n">
+        <v>292.751742</v>
+      </c>
+      <c r="F79" t="n">
+        <v>10.824315</v>
+      </c>
+      <c r="G79" t="n">
+        <v>8.783059</v>
+      </c>
+      <c r="H79" t="n">
+        <v>17.272437</v>
+      </c>
+      <c r="I79" t="n">
+        <v>1</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.7127776445109902</v>
+      </c>
+      <c r="L79" t="n">
+        <v>42.977436</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0.7127776445109902</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>NCAA</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>27.152528</v>
+      </c>
+      <c r="D80" t="n">
+        <v>20.122844</v>
+      </c>
+      <c r="E80" t="n">
+        <v>254.86498</v>
+      </c>
+      <c r="F80" t="n">
+        <v>4.062789</v>
+      </c>
+      <c r="G80" t="n">
+        <v>9.424991</v>
+      </c>
+      <c r="H80" t="n">
+        <v>17.476565</v>
+      </c>
+      <c r="I80" t="n">
+        <v>1</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.720109559102335</v>
+      </c>
+      <c r="L80" t="n">
+        <v>30.416383</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0.720109559102335</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>NCAA</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>27.152528</v>
+      </c>
+      <c r="D81" t="n">
+        <v>2.396691</v>
+      </c>
+      <c r="E81" t="n">
+        <v>6789.084786</v>
+      </c>
+      <c r="F81" t="n">
+        <v>29.011541</v>
+      </c>
+      <c r="G81" t="n">
+        <v>3.506387</v>
+      </c>
+      <c r="H81" t="n">
+        <v>554.2202319999999</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0.9148343153139122</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0.5164218840632655</v>
+      </c>
+      <c r="L81" t="n">
+        <v>8.299769000000001</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0.5164218840632655</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>OMOP_CDM_dayz</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Out of Memory Error</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
+        <v>3.60112</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0.9178820705894528</v>
+      </c>
+      <c r="N82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>OMOP_CDM_dayz</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>3.460992</v>
+      </c>
+      <c r="D83" t="n">
+        <v>46.746206</v>
+      </c>
+      <c r="E83" t="n">
+        <v>178.096815</v>
+      </c>
+      <c r="F83" t="n">
+        <v>22.480538</v>
+      </c>
+      <c r="G83" t="n">
+        <v>35.558943</v>
+      </c>
+      <c r="H83" t="n">
+        <v>33.662359</v>
+      </c>
+      <c r="I83" t="n">
+        <v>1</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0.9679094214148942</v>
+      </c>
+      <c r="L83" t="n">
+        <v>85.90626900000001</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0.9679094214148942</v>
+      </c>
+      <c r="N83" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>OMOP_CDM_dayz</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>3.460992</v>
+      </c>
+      <c r="D84" t="n">
+        <v>28.95532</v>
+      </c>
+      <c r="E84" t="n">
+        <v>123.483496</v>
+      </c>
+      <c r="F84" t="n">
+        <v>15.347955</v>
+      </c>
+      <c r="G84" t="n">
+        <v>28.400839</v>
+      </c>
+      <c r="H84" t="n">
+        <v>33.799413</v>
+      </c>
+      <c r="I84" t="n">
+        <v>1</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0.9588474098224912</v>
+      </c>
+      <c r="L84" t="n">
+        <v>60.957279</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0.9588474098224912</v>
+      </c>
+      <c r="N84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>OMOP_CDM_dayz</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>3.460992</v>
+      </c>
+      <c r="D85" t="n">
+        <v>3.60112</v>
+      </c>
+      <c r="E85" t="n">
+        <v>24.896124</v>
+      </c>
+      <c r="F85" t="n">
+        <v>5.167355</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0.642719</v>
+      </c>
+      <c r="H85" t="n">
+        <v>34.047004</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0.9268371517027864</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0.9178820705894528</v>
+      </c>
+      <c r="L85" t="n">
+        <v>7.844958999999999</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0.9178820705894528</v>
+      </c>
+      <c r="N85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>PTE</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>0.95856</v>
+      </c>
+      <c r="D86" t="n">
+        <v>2481.110933</v>
+      </c>
+      <c r="E86" t="n">
+        <v>1452.990808</v>
+      </c>
+      <c r="F86" t="n">
+        <v>15.802101</v>
+      </c>
+      <c r="G86" t="n">
+        <v>4914.269472</v>
+      </c>
+      <c r="H86" t="n">
+        <v>1.033545</v>
+      </c>
+      <c r="I86" t="n">
+        <v>1</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0.6015878629259466</v>
+      </c>
+      <c r="L86" t="n">
+        <v>7396.070449999999</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0.6015878629259466</v>
+      </c>
+      <c r="N86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>PTE</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>0.95856</v>
+      </c>
+      <c r="D87" t="n">
+        <v>18.528523</v>
+      </c>
+      <c r="E87" t="n">
+        <v>113.921341</v>
+      </c>
+      <c r="F87" t="n">
+        <v>14.455717</v>
+      </c>
+      <c r="G87" t="n">
+        <v>3.745181</v>
+      </c>
+      <c r="H87" t="n">
+        <v>1.047497</v>
+      </c>
+      <c r="I87" t="n">
+        <v>1</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0.6197741033070919</v>
+      </c>
+      <c r="L87" t="n">
+        <v>23.022537</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0.6197741033070919</v>
+      </c>
+      <c r="N87" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>PTE</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>0.95856</v>
+      </c>
+      <c r="D88" t="n">
+        <v>12.746198</v>
+      </c>
+      <c r="E88" t="n">
+        <v>105.228629</v>
+      </c>
+      <c r="F88" t="n">
+        <v>11.911301</v>
+      </c>
+      <c r="G88" t="n">
+        <v>2.093028</v>
+      </c>
+      <c r="H88" t="n">
+        <v>1.054456</v>
+      </c>
+      <c r="I88" t="n">
+        <v>1</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0.608733054709825</v>
+      </c>
+      <c r="L88" t="n">
+        <v>15.588059</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0.608733054709825</v>
+      </c>
+      <c r="N88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>PTE</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>0.95856</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0.690045</v>
+      </c>
+      <c r="E89" t="n">
+        <v>5.710268</v>
+      </c>
+      <c r="F89" t="n">
+        <v>1.190468</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0.154947</v>
+      </c>
+      <c r="H89" t="n">
+        <v>1.004986</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0.8758072662901631</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0.4312415874112958</v>
+      </c>
+      <c r="L89" t="n">
+        <v>1.535037</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0.4312415874112958</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Pima</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>0.111744</v>
+      </c>
+      <c r="D90" t="n">
+        <v>667.225955</v>
+      </c>
+      <c r="E90" t="n">
+        <v>39.33468</v>
+      </c>
+      <c r="F90" t="n">
+        <v>3.37678</v>
+      </c>
+      <c r="G90" t="n">
+        <v>728.473941</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0.2436559999999999</v>
+      </c>
+      <c r="I90" t="n">
+        <v>1</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0.8703703703703703</v>
+      </c>
+      <c r="L90" t="n">
+        <v>1396.031742</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0.8703703703703703</v>
+      </c>
+      <c r="N90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Pima</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>0.111744</v>
+      </c>
+      <c r="D91" t="n">
+        <v>4.542514</v>
+      </c>
+      <c r="E91" t="n">
+        <v>27.280683</v>
+      </c>
+      <c r="F91" t="n">
+        <v>3.427866</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0.792215</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0.250915</v>
+      </c>
+      <c r="I91" t="n">
+        <v>1</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0.8795331790123457</v>
+      </c>
+      <c r="L91" t="n">
+        <v>5.711414</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0.8795331790123457</v>
+      </c>
+      <c r="N91" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Pima</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>0.111744</v>
+      </c>
+      <c r="D92" t="n">
+        <v>2.764766</v>
+      </c>
+      <c r="E92" t="n">
+        <v>31.570519</v>
+      </c>
+      <c r="F92" t="n">
+        <v>2.986137</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0.335123</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0.256741</v>
+      </c>
+      <c r="I92" t="n">
+        <v>1</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0.8731192129629629</v>
+      </c>
+      <c r="L92" t="n">
+        <v>3.476574</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0.8731192129629629</v>
+      </c>
+      <c r="N92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Pima</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>0.111744</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0.331846</v>
+      </c>
+      <c r="E93" t="n">
+        <v>1.32798</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0.195529</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0.081737</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0.246909</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0.821261935763889</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0.5798162348974403</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0.7454289999999999</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0.5798162348974403</v>
+      </c>
+      <c r="N93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>PremierLeague</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Out of Memory Error</t>
+        </is>
+      </c>
+      <c r="L94" t="n">
+        <v>1.356684</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0.3018133168276543</v>
+      </c>
+      <c r="N94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>PremierLeague</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>17.2018</v>
+      </c>
+      <c r="D95" t="n">
+        <v>28.45794</v>
+      </c>
+      <c r="E95" t="n">
+        <v>238.755777</v>
+      </c>
+      <c r="F95" t="n">
+        <v>4.831872</v>
+      </c>
+      <c r="G95" t="n">
+        <v>7.02822</v>
+      </c>
+      <c r="H95" t="n">
+        <v>92.264595</v>
+      </c>
+      <c r="I95" t="n">
+        <v>1</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0.7566995115606292</v>
+      </c>
+      <c r="L95" t="n">
+        <v>36.842844</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0.7566995115606292</v>
+      </c>
+      <c r="N95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>PremierLeague</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>17.2018</v>
+      </c>
+      <c r="D96" t="n">
+        <v>26.009266</v>
+      </c>
+      <c r="E96" t="n">
+        <v>217.971833</v>
+      </c>
+      <c r="F96" t="n">
+        <v>4.351478</v>
+      </c>
+      <c r="G96" t="n">
+        <v>9.530086000000001</v>
+      </c>
+      <c r="H96" t="n">
+        <v>92.928077</v>
+      </c>
+      <c r="I96" t="n">
+        <v>1</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0.7586691952052512</v>
+      </c>
+      <c r="L96" t="n">
+        <v>36.896036</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0.7586691952052512</v>
+      </c>
+      <c r="N96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>PremierLeague</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>17.2018</v>
+      </c>
+      <c r="D97" t="n">
+        <v>1.356684</v>
+      </c>
+      <c r="E97" t="n">
+        <v>87.19672799999999</v>
+      </c>
+      <c r="F97" t="n">
+        <v>17.242987</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0.303165</v>
+      </c>
+      <c r="H97" t="n">
+        <v>103.895528</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0.7187755791609591</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0.3018133168276543</v>
+      </c>
+      <c r="L97" t="n">
+        <v>3.016533</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0.3018133168276543</v>
+      </c>
+      <c r="N97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Pyrimidine</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>0.022752</v>
+      </c>
+      <c r="D98" t="n">
+        <v>10.796199</v>
+      </c>
+      <c r="E98" t="n">
+        <v>24.413278</v>
+      </c>
+      <c r="F98" t="n">
+        <v>2.198936</v>
+      </c>
+      <c r="G98" t="n">
+        <v>18.047552</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0.286274</v>
+      </c>
+      <c r="I98" t="n">
+        <v>1</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0.8311226316894292</v>
+      </c>
+      <c r="L98" t="n">
+        <v>29.215702</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0.8311226316894292</v>
+      </c>
+      <c r="N98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Pyrimidine</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>0.022752</v>
+      </c>
+      <c r="D99" t="n">
+        <v>1.643135</v>
+      </c>
+      <c r="E99" t="n">
+        <v>8.772055</v>
+      </c>
+      <c r="F99" t="n">
+        <v>1.157768</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0.306924</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0.280962</v>
+      </c>
+      <c r="I99" t="n">
+        <v>1</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0.8224644973264432</v>
+      </c>
+      <c r="L99" t="n">
+        <v>2.347874</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0.8224644973264432</v>
+      </c>
+      <c r="N99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Pyrimidine</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>0.022752</v>
+      </c>
+      <c r="D100" t="n">
+        <v>1.069361</v>
+      </c>
+      <c r="E100" t="n">
+        <v>10.165465</v>
+      </c>
+      <c r="F100" t="n">
+        <v>1.086105</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0.214213</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0.284116</v>
+      </c>
+      <c r="I100" t="n">
+        <v>1</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0.8315310898077607</v>
+      </c>
+      <c r="L100" t="n">
+        <v>1.681389</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0.8315310898077607</v>
+      </c>
+      <c r="N100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Pyrimidine</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>0.022752</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0.371951</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.562797</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0.13585</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0.08706700000000001</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0.283412</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0.809020559020559</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0.5138749409178033</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0.830969</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0.5138749409178033</v>
+      </c>
+      <c r="N101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>148.44064</v>
+      </c>
+      <c r="D102" t="n">
+        <v>51420.135705</v>
+      </c>
+      <c r="E102" t="n">
+        <v>2277.350943</v>
+      </c>
+      <c r="F102" t="n">
+        <v>11.214965</v>
+      </c>
+      <c r="G102" t="n">
+        <v>127825.629554</v>
+      </c>
+      <c r="H102" t="n">
+        <v>30.379977</v>
+      </c>
+      <c r="I102" t="n">
+        <v>1</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0.8440387456684261</v>
+      </c>
+      <c r="L102" t="n">
+        <v>179247.925467</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0.8440387456684261</v>
+      </c>
+      <c r="N102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>148.44064</v>
+      </c>
+      <c r="D103" t="n">
+        <v>206.776347</v>
+      </c>
+      <c r="E103" t="n">
+        <v>1663.028531</v>
+      </c>
+      <c r="F103" t="n">
+        <v>78.03652</v>
+      </c>
+      <c r="G103" t="n">
+        <v>176.33291</v>
+      </c>
+      <c r="H103" t="n">
+        <v>32.218158</v>
+      </c>
+      <c r="I103" t="n">
+        <v>1</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0.8853482368944174</v>
+      </c>
+      <c r="L103" t="n">
+        <v>385.573983</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0.8853482368944174</v>
+      </c>
+      <c r="N103" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>148.44064</v>
+      </c>
+      <c r="D104" t="n">
+        <v>124.610415</v>
+      </c>
+      <c r="E104" t="n">
+        <v>1146.286202</v>
+      </c>
+      <c r="F104" t="n">
+        <v>1.996169</v>
+      </c>
+      <c r="G104" t="n">
+        <v>175.984489</v>
+      </c>
+      <c r="H104" t="n">
+        <v>32.593967</v>
+      </c>
+      <c r="I104" t="n">
+        <v>1</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0.8682522175583455</v>
+      </c>
+      <c r="L104" t="n">
+        <v>303.05963</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0.8682522175583455</v>
+      </c>
+      <c r="N104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>148.44064</v>
+      </c>
+      <c r="D105" t="n">
+        <v>2.160208</v>
+      </c>
+      <c r="E105" t="n">
+        <v>659.815761</v>
+      </c>
+      <c r="F105" t="n">
+        <v>131.800237</v>
+      </c>
+      <c r="G105" t="n">
+        <v>1.1566</v>
+      </c>
+      <c r="H105" t="n">
+        <v>29.038779</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0.9260321530033698</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0.7136837708167004</v>
+      </c>
+      <c r="L105" t="n">
+        <v>5.477016</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0.7136837708167004</v>
+      </c>
+      <c r="N105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>0.32244</v>
+      </c>
+      <c r="D106" t="n">
+        <v>99.679232</v>
+      </c>
+      <c r="E106" t="n">
+        <v>100.31818</v>
+      </c>
+      <c r="F106" t="n">
+        <v>11.55804</v>
+      </c>
+      <c r="G106" t="n">
+        <v>3763.917005</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0.944115</v>
+      </c>
+      <c r="I106" t="n">
+        <v>1</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0.7852335164835165</v>
+      </c>
+      <c r="L106" t="n">
+        <v>3864.225317</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0.7852335164835165</v>
+      </c>
+      <c r="N106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>0.32244</v>
+      </c>
+      <c r="D107" t="n">
+        <v>17.358522</v>
+      </c>
+      <c r="E107" t="n">
+        <v>106.502789</v>
+      </c>
+      <c r="F107" t="n">
+        <v>13.313338</v>
+      </c>
+      <c r="G107" t="n">
+        <v>3.881324</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0.965608</v>
+      </c>
+      <c r="I107" t="n">
+        <v>1</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0.954052197802198</v>
+      </c>
+      <c r="L107" t="n">
+        <v>21.900289</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0.954052197802198</v>
+      </c>
+      <c r="N107" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>0.32244</v>
+      </c>
+      <c r="D108" t="n">
+        <v>10.83677</v>
+      </c>
+      <c r="E108" t="n">
+        <v>97.90018999999999</v>
+      </c>
+      <c r="F108" t="n">
+        <v>10.456642</v>
+      </c>
+      <c r="G108" t="n">
+        <v>1.335355</v>
+      </c>
+      <c r="H108" t="n">
+        <v>1.312469</v>
+      </c>
+      <c r="I108" t="n">
+        <v>1</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0.8709478021978021</v>
+      </c>
+      <c r="L108" t="n">
+        <v>12.832568</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0.8709478021978021</v>
+      </c>
+      <c r="N108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>0.32244</v>
+      </c>
+      <c r="D109" t="n">
+        <v>0.62908</v>
+      </c>
+      <c r="E109" t="n">
+        <v>1.495081</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0.281823</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0.09346</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0.954801</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0.8684414265141521</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0.7696537782005981</v>
+      </c>
+      <c r="L109" t="n">
+        <v>1.35162</v>
+      </c>
+      <c r="M109" t="n">
+        <v>0.7696537782005981</v>
+      </c>
+      <c r="N109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>SalesDB</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Synthesizer Timeout</t>
+        </is>
+      </c>
+      <c r="L110" t="n">
+        <v>345603.127422</v>
+      </c>
+      <c r="M110" t="n">
+        <v>0.2783622343636465</v>
+      </c>
+      <c r="N110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>SalesDB</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>269.254472</v>
+      </c>
+      <c r="D111" t="n">
+        <v>268.501185</v>
+      </c>
+      <c r="E111" t="n">
+        <v>3865.395265</v>
+      </c>
+      <c r="F111" t="n">
+        <v>136.894337</v>
+      </c>
+      <c r="G111" t="n">
+        <v>377.134091</v>
+      </c>
+      <c r="H111" t="n">
+        <v>17.883164</v>
+      </c>
+      <c r="I111" t="n">
+        <v>1</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0.4373896662388113</v>
+      </c>
+      <c r="L111" t="n">
+        <v>646.36931</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0.4373896662388113</v>
+      </c>
+      <c r="N111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>SalesDB</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>269.254472</v>
+      </c>
+      <c r="D112" t="n">
+        <v>44.622195</v>
+      </c>
+      <c r="E112" t="n">
+        <v>2188.124673</v>
+      </c>
+      <c r="F112" t="n">
+        <v>1.939392</v>
+      </c>
+      <c r="G112" t="n">
+        <v>335.415596</v>
+      </c>
+      <c r="H112" t="n">
+        <v>18.185302</v>
+      </c>
+      <c r="I112" t="n">
+        <v>1</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0.493079680171551</v>
+      </c>
+      <c r="L112" t="n">
+        <v>380.771825</v>
+      </c>
+      <c r="M112" t="n">
+        <v>0.493079680171551</v>
+      </c>
+      <c r="N112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>SalesDB</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>269.254472</v>
+      </c>
+      <c r="D113" t="n">
+        <v>1.165704</v>
+      </c>
+      <c r="E113" t="n">
+        <v>2414.406685</v>
+      </c>
+      <c r="F113" t="n">
+        <v>269.133272</v>
+      </c>
+      <c r="G113" t="n">
+        <v>1.961718</v>
+      </c>
+      <c r="H113" t="n">
+        <v>29.602807</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0.8964491515754288</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0.2783622343636465</v>
+      </c>
+      <c r="L113" t="n">
+        <v>4.293126</v>
+      </c>
+      <c r="M113" t="n">
+        <v>0.2783622343636465</v>
+      </c>
+      <c r="N113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Same_gen</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>0.045272</v>
+      </c>
+      <c r="D114" t="n">
+        <v>12.174757</v>
+      </c>
+      <c r="E114" t="n">
+        <v>27.194331</v>
+      </c>
+      <c r="F114" t="n">
+        <v>1.699909</v>
+      </c>
+      <c r="G114" t="n">
+        <v>35.191592</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0.12046</v>
+      </c>
+      <c r="I114" t="n">
+        <v>1</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0.8640148011100832</v>
+      </c>
+      <c r="L114" t="n">
+        <v>47.43801</v>
+      </c>
+      <c r="M114" t="n">
+        <v>0.8640148011100832</v>
+      </c>
+      <c r="N114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Same_gen</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>0.045272</v>
+      </c>
+      <c r="D115" t="n">
+        <v>1.725855</v>
+      </c>
+      <c r="E115" t="n">
+        <v>16.877236</v>
+      </c>
+      <c r="F115" t="n">
+        <v>1.845398</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0.416947</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0.109571</v>
+      </c>
+      <c r="I115" t="n">
+        <v>1</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0.9573697193956214</v>
+      </c>
+      <c r="L115" t="n">
+        <v>2.214273</v>
+      </c>
+      <c r="M115" t="n">
+        <v>0.9573697193956214</v>
+      </c>
+      <c r="N115" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Same_gen</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>0.045272</v>
+      </c>
+      <c r="D116" t="n">
+        <v>1.525493</v>
+      </c>
+      <c r="E116" t="n">
+        <v>16.010592</v>
+      </c>
+      <c r="F116" t="n">
+        <v>1.537179</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0.151407</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0.109927</v>
+      </c>
+      <c r="I116" t="n">
+        <v>1</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0.8956213382670367</v>
+      </c>
+      <c r="L116" t="n">
+        <v>1.748371</v>
+      </c>
+      <c r="M116" t="n">
+        <v>0.8956213382670367</v>
+      </c>
+      <c r="N116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Same_gen</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>0.045272</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.071661</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.367408</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.049976</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.014379</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.116491</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.8354487647216305</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.6943416589577551</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.157701</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.6943416589577551</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Student_loan</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>0.090688</v>
+      </c>
+      <c r="D118" t="n">
+        <v>253.295917</v>
+      </c>
+      <c r="E118" t="n">
+        <v>35.099681</v>
+      </c>
+      <c r="F118" t="n">
+        <v>3.584074</v>
+      </c>
+      <c r="G118" t="n">
+        <v>881.284151</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.214723</v>
+      </c>
+      <c r="I118" t="n">
+        <v>1</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.8695527843465695</v>
+      </c>
+      <c r="L118" t="n">
+        <v>1134.68178</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.8695527843465695</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Student_loan</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>0.090688</v>
+      </c>
+      <c r="D119" t="n">
+        <v>4.362231</v>
+      </c>
+      <c r="E119" t="n">
+        <v>36.832441</v>
+      </c>
+      <c r="F119" t="n">
+        <v>3.867512</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.811226</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.208299</v>
+      </c>
+      <c r="I119" t="n">
+        <v>1</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.9454135177521596</v>
+      </c>
+      <c r="L119" t="n">
+        <v>5.290018</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.9454135177521596</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Student_loan</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>0.090688</v>
+      </c>
+      <c r="D120" t="n">
+        <v>3.138534</v>
+      </c>
+      <c r="E120" t="n">
+        <v>27.845812</v>
+      </c>
+      <c r="F120" t="n">
+        <v>3.291698</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.420168</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.216032</v>
+      </c>
+      <c r="I120" t="n">
+        <v>1</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.9464389102374616</v>
+      </c>
+      <c r="L120" t="n">
+        <v>3.675263</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.9464389102374616</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Student_loan</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>0.090688</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.101712</v>
+      </c>
+      <c r="E121" t="n">
+        <v>1.059504</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.121201</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.025197</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.214102</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.8217628699132877</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.8324635308897428</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.228621</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.8324635308897428</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Toxicology</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>1.030392</v>
+      </c>
+      <c r="D122" t="n">
+        <v>140.836646</v>
+      </c>
+      <c r="E122" t="n">
+        <v>2714.568222</v>
+      </c>
+      <c r="F122" t="n">
+        <v>1.975327</v>
+      </c>
+      <c r="G122" t="n">
+        <v>4891.373492</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.27773</v>
+      </c>
+      <c r="I122" t="n">
+        <v>1</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.8837868904691255</v>
+      </c>
+      <c r="L122" t="n">
+        <v>5032.28541</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.8837868904691255</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Toxicology</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>1.030392</v>
+      </c>
+      <c r="D123" t="n">
+        <v>4.228273</v>
+      </c>
+      <c r="E123" t="n">
+        <v>24.540094</v>
+      </c>
+      <c r="F123" t="n">
+        <v>2.702842</v>
+      </c>
+      <c r="G123" t="n">
+        <v>1.035804</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.277093</v>
+      </c>
+      <c r="I123" t="n">
+        <v>1</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.9857502927263728</v>
+      </c>
+      <c r="L123" t="n">
+        <v>5.344968</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.9857502927263728</v>
+      </c>
+      <c r="N123" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Toxicology</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>1.030392</v>
+      </c>
+      <c r="D124" t="n">
+        <v>1.730364</v>
+      </c>
+      <c r="E124" t="n">
+        <v>17.412139</v>
+      </c>
+      <c r="F124" t="n">
+        <v>1.561064</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.776765</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.287666</v>
+      </c>
+      <c r="I124" t="n">
+        <v>1</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.9412180394218286</v>
+      </c>
+      <c r="L124" t="n">
+        <v>2.58802</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.9412180394218286</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Toxicology</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>1.030392</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.07527200000000001</v>
+      </c>
+      <c r="E125" t="n">
+        <v>5.824985</v>
+      </c>
+      <c r="F125" t="n">
+        <v>1.210419</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.027127</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.262117</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.8424803632428125</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.6477606385133192</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.177671</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.6477606385133192</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Triazine</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>0.119296</v>
+      </c>
+      <c r="D126" t="n">
+        <v>23.721183</v>
+      </c>
+      <c r="E126" t="n">
+        <v>26.680166</v>
+      </c>
+      <c r="F126" t="n">
+        <v>2.423082</v>
+      </c>
+      <c r="G126" t="n">
+        <v>47.247682</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.354929</v>
+      </c>
+      <c r="I126" t="n">
+        <v>1</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.8922244552469664</v>
+      </c>
+      <c r="L126" t="n">
+        <v>71.344897</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.8922244552469664</v>
+      </c>
+      <c r="N126" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Triazine</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>0.119296</v>
+      </c>
+      <c r="D127" t="n">
+        <v>1.46647</v>
+      </c>
+      <c r="E127" t="n">
+        <v>10.599158</v>
+      </c>
+      <c r="F127" t="n">
+        <v>1.186271</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.307537</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.360743</v>
+      </c>
+      <c r="I127" t="n">
+        <v>1</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.8052235787898532</v>
+      </c>
+      <c r="L127" t="n">
+        <v>2.207931</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.8052235787898532</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Triazine</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>0.119296</v>
+      </c>
+      <c r="D128" t="n">
+        <v>1.191085</v>
+      </c>
+      <c r="E128" t="n">
+        <v>10.301639</v>
+      </c>
+      <c r="F128" t="n">
+        <v>1.09795</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.274007</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.3627499999999999</v>
+      </c>
+      <c r="I128" t="n">
+        <v>1</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.8067169274452534</v>
+      </c>
+      <c r="L128" t="n">
+        <v>1.899016</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.8067169274452534</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Triazine</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>0.119296</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.376032</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.902487</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.242577</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.09658</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.354305</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.7808926437958696</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.5143888003277249</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.848644</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.5143888003277249</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>TubePricing</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>9.670944</v>
+      </c>
+      <c r="D130" t="n">
+        <v>9804.394609000001</v>
+      </c>
+      <c r="E130" t="n">
+        <v>15588.417126</v>
+      </c>
+      <c r="F130" t="n">
+        <v>511.170917</v>
+      </c>
+      <c r="G130" t="n">
+        <v>68549.701462</v>
+      </c>
+      <c r="H130" t="n">
+        <v>332.484083</v>
+      </c>
+      <c r="I130" t="n">
+        <v>1</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.5495273088764041</v>
+      </c>
+      <c r="L130" t="n">
+        <v>78365.08998799999</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.5495273088764041</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>TubePricing</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>9.670944</v>
+      </c>
+      <c r="D131" t="n">
+        <v>32.230358</v>
+      </c>
+      <c r="E131" t="n">
+        <v>122.810223</v>
+      </c>
+      <c r="F131" t="n">
+        <v>11.612711</v>
+      </c>
+      <c r="G131" t="n">
+        <v>7.977091</v>
+      </c>
+      <c r="H131" t="n">
+        <v>10.554086</v>
+      </c>
+      <c r="I131" t="n">
+        <v>1</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.5736597759693398</v>
+      </c>
+      <c r="L131" t="n">
+        <v>44.034649</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.5736597759693398</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>TubePricing</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>9.670944</v>
+      </c>
+      <c r="D132" t="n">
+        <v>21.05212</v>
+      </c>
+      <c r="E132" t="n">
+        <v>112.108463</v>
+      </c>
+      <c r="F132" t="n">
+        <v>8.178234</v>
+      </c>
+      <c r="G132" t="n">
+        <v>7.606863</v>
+      </c>
+      <c r="H132" t="n">
+        <v>10.62909</v>
+      </c>
+      <c r="I132" t="n">
+        <v>1</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.577069722568228</v>
+      </c>
+      <c r="L132" t="n">
+        <v>32.486183</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.577069722568228</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>TubePricing</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>9.670944</v>
+      </c>
+      <c r="D133" t="n">
+        <v>10.993917</v>
+      </c>
+      <c r="E133" t="n">
+        <v>148.17728</v>
+      </c>
+      <c r="F133" t="n">
+        <v>9.307684999999999</v>
+      </c>
+      <c r="G133" t="n">
+        <v>5.548704</v>
+      </c>
+      <c r="H133" t="n">
+        <v>346.238604</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.9321997327053227</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.4786925588915128</v>
+      </c>
+      <c r="L133" t="n">
+        <v>27.536538</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.4786925588915128</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>UTube</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>0.114032</v>
+      </c>
+      <c r="D134" t="n">
+        <v>61.433783</v>
+      </c>
+      <c r="E134" t="n">
+        <v>24.437274</v>
+      </c>
+      <c r="F134" t="n">
+        <v>1.264446</v>
+      </c>
+      <c r="G134" t="n">
+        <v>94.141048</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.09075999999999999</v>
+      </c>
+      <c r="I134" t="n">
+        <v>1</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.8276064058781456</v>
+      </c>
+      <c r="L134" t="n">
+        <v>155.623788</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.8276064058781456</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>UTube</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>0.114032</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.283891</v>
+      </c>
+      <c r="E135" t="n">
+        <v>10.53885</v>
+      </c>
+      <c r="F135" t="n">
+        <v>1.134615</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.244739</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.090374</v>
+      </c>
+      <c r="I135" t="n">
+        <v>1</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.9120841819477176</v>
+      </c>
+      <c r="L135" t="n">
+        <v>1.579808</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.9120841819477176</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>UTube</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>0.114032</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.992968</v>
+      </c>
+      <c r="E136" t="n">
+        <v>10.142899</v>
+      </c>
+      <c r="F136" t="n">
+        <v>1.018112</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.187518</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.09310099999999991</v>
+      </c>
+      <c r="I136" t="n">
+        <v>1</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.913533099608314</v>
+      </c>
+      <c r="L136" t="n">
+        <v>1.231664</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.913533099608314</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>UTube</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>0.114032</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.048957</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.61015</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.09595099999999999</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.010032</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.08824</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.7738639331418126</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.6136551366081909</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.107946</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.6136551366081909</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>UW_std</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>0.023216</v>
+      </c>
+      <c r="D138" t="n">
+        <v>3.137245</v>
+      </c>
+      <c r="E138" t="n">
+        <v>24.969951</v>
+      </c>
+      <c r="F138" t="n">
+        <v>1.682004</v>
+      </c>
+      <c r="G138" t="n">
+        <v>107.832891</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.155973</v>
+      </c>
+      <c r="I138" t="n">
+        <v>1</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.8704884577186736</v>
+      </c>
+      <c r="L138" t="n">
+        <v>111.080512</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.8704884577186736</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>UW_std</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>0.023216</v>
+      </c>
+      <c r="D139" t="n">
+        <v>2.117103</v>
+      </c>
+      <c r="E139" t="n">
+        <v>17.017581</v>
+      </c>
+      <c r="F139" t="n">
+        <v>1.830702</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.403542</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.154172</v>
+      </c>
+      <c r="I139" t="n">
+        <v>1</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.8917078458445366</v>
+      </c>
+      <c r="L139" t="n">
+        <v>2.632434</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.8917078458445366</v>
+      </c>
+      <c r="N139" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>UW_std</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>0.023216</v>
+      </c>
+      <c r="D140" t="n">
+        <v>1.663882</v>
+      </c>
+      <c r="E140" t="n">
+        <v>12.673471</v>
+      </c>
+      <c r="F140" t="n">
+        <v>1.618017</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.230033</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.143477</v>
+      </c>
+      <c r="I140" t="n">
+        <v>1</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.885266029600562</v>
+      </c>
+      <c r="L140" t="n">
+        <v>2.005704</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.885266029600562</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>UW_std</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>0.023216</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.110376</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.178205</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.023226</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.015373</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.154954</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.8779475063783014</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.658087581385933</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.236125</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.658087581385933</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>WebKP</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>1.957768</v>
+      </c>
+      <c r="D142" t="n">
+        <v>107.54012</v>
+      </c>
+      <c r="E142" t="n">
+        <v>47.721732</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.470783</v>
+      </c>
+      <c r="G142" t="n">
+        <v>345.80786</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.327229</v>
+      </c>
+      <c r="I142" t="n">
+        <v>1</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.7863318545683656</v>
+      </c>
+      <c r="L142" t="n">
+        <v>453.435173</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.7863318545683656</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>WebKP</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>1.957768</v>
+      </c>
+      <c r="D143" t="n">
+        <v>5.436724</v>
+      </c>
+      <c r="E143" t="n">
+        <v>37.821345</v>
+      </c>
+      <c r="F143" t="n">
+        <v>7.017378</v>
+      </c>
+      <c r="G143" t="n">
+        <v>1.362589</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.301029</v>
+      </c>
+      <c r="I143" t="n">
+        <v>1</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.8818696555539202</v>
+      </c>
+      <c r="L143" t="n">
+        <v>6.884664</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.8818696555539202</v>
+      </c>
+      <c r="N143" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>WebKP</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>1.957768</v>
+      </c>
+      <c r="D144" t="n">
+        <v>2.315393</v>
+      </c>
+      <c r="E144" t="n">
+        <v>29.032918</v>
+      </c>
+      <c r="F144" t="n">
+        <v>1.420043</v>
+      </c>
+      <c r="G144" t="n">
+        <v>1.153244</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0.294271</v>
+      </c>
+      <c r="I144" t="n">
+        <v>1</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0.8515590385821631</v>
+      </c>
+      <c r="L144" t="n">
+        <v>3.553988</v>
+      </c>
+      <c r="M144" t="n">
+        <v>0.8515590385821631</v>
+      </c>
+      <c r="N144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>WebKP</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>1.957768</v>
+      </c>
+      <c r="D145" t="n">
+        <v>0.08719300000000001</v>
+      </c>
+      <c r="E145" t="n">
+        <v>12.991554</v>
+      </c>
+      <c r="F145" t="n">
+        <v>5.647392</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0.050155</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0.317706</v>
+      </c>
+      <c r="I145" t="n">
+        <v>0.8625594065370525</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0.5930670513382034</v>
+      </c>
+      <c r="L145" t="n">
+        <v>0.224541</v>
+      </c>
+      <c r="M145" t="n">
+        <v>0.5930670513382034</v>
+      </c>
+      <c r="N145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>airbnb-simplified</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Synthesizer Timeout</t>
+        </is>
+      </c>
+      <c r="L146" t="n">
+        <v>345676.906609</v>
+      </c>
+      <c r="M146" t="n">
+        <v>0.3762545255304155</v>
+      </c>
+      <c r="N146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>airbnb-simplified</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>293.14392</v>
+      </c>
+      <c r="D147" t="n">
+        <v>553.598071</v>
+      </c>
+      <c r="E147" t="n">
+        <v>4208.142978</v>
+      </c>
+      <c r="F147" t="n">
+        <v>28.230867</v>
+      </c>
+      <c r="G147" t="n">
+        <v>196.781506</v>
+      </c>
+      <c r="H147" t="n">
+        <v>73.211868</v>
+      </c>
+      <c r="I147" t="n">
+        <v>1</v>
+      </c>
+      <c r="J147" t="n">
+        <v>0.6050169406809366</v>
+      </c>
+      <c r="L147" t="n">
+        <v>755.7428580000001</v>
+      </c>
+      <c r="M147" t="n">
+        <v>0.6050169406809366</v>
+      </c>
+      <c r="N147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>airbnb-simplified</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>293.14392</v>
+      </c>
+      <c r="D148" t="n">
+        <v>435.022048</v>
+      </c>
+      <c r="E148" t="n">
+        <v>2964.754733</v>
+      </c>
+      <c r="F148" t="n">
+        <v>1.228296</v>
+      </c>
+      <c r="G148" t="n">
+        <v>194.689633</v>
+      </c>
+      <c r="H148" t="n">
+        <v>72.89757499999999</v>
+      </c>
+      <c r="I148" t="n">
+        <v>1</v>
+      </c>
+      <c r="J148" t="n">
+        <v>0.7367952180951104</v>
+      </c>
+      <c r="L148" t="n">
+        <v>635.0749619999999</v>
+      </c>
+      <c r="M148" t="n">
+        <v>0.7367952180951104</v>
+      </c>
+      <c r="N148" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>airbnb-simplified</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>293.14392</v>
+      </c>
+      <c r="D149" t="n">
+        <v>44.448117</v>
+      </c>
+      <c r="E149" t="n">
+        <v>3285.291571</v>
+      </c>
+      <c r="F149" t="n">
+        <v>212.870928</v>
+      </c>
+      <c r="G149" t="n">
+        <v>32.458492</v>
+      </c>
+      <c r="H149" t="n">
+        <v>257.063795</v>
+      </c>
+      <c r="I149" t="n">
+        <v>0.9274696331475896</v>
+      </c>
+      <c r="J149" t="n">
+        <v>0.3762545255304155</v>
+      </c>
+      <c r="L149" t="n">
+        <v>121.354726</v>
+      </c>
+      <c r="M149" t="n">
+        <v>0.3762545255304155</v>
+      </c>
+      <c r="N149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>fake_hotels</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>0.04869</v>
+      </c>
+      <c r="D150" t="n">
+        <v>27.69632</v>
+      </c>
+      <c r="E150" t="n">
+        <v>49.772699</v>
+      </c>
+      <c r="F150" t="n">
+        <v>1.583609</v>
+      </c>
+      <c r="G150" t="n">
+        <v>3.874817</v>
+      </c>
+      <c r="H150" t="n">
+        <v>0.268664</v>
+      </c>
+      <c r="I150" t="n">
+        <v>1</v>
+      </c>
+      <c r="J150" t="n">
+        <v>0.6276139352031315</v>
+      </c>
+      <c r="L150" t="n">
+        <v>31.768444</v>
+      </c>
+      <c r="M150" t="n">
+        <v>0.6276139352031315</v>
+      </c>
+      <c r="N150" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>fake_hotels</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>0.04869</v>
+      </c>
+      <c r="D151" t="n">
+        <v>26.487325</v>
+      </c>
+      <c r="E151" t="n">
+        <v>41.256369</v>
+      </c>
+      <c r="F151" t="n">
+        <v>1.210442</v>
+      </c>
+      <c r="G151" t="n">
+        <v>2.068767</v>
+      </c>
+      <c r="H151" t="n">
+        <v>0.263334</v>
+      </c>
+      <c r="I151" t="n">
+        <v>1</v>
+      </c>
+      <c r="J151" t="n">
+        <v>0.6834125588396149</v>
+      </c>
+      <c r="L151" t="n">
+        <v>28.765052</v>
+      </c>
+      <c r="M151" t="n">
+        <v>0.6834125588396149</v>
+      </c>
+      <c r="N151" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>fake_hotels</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>0.04869</v>
+      </c>
+      <c r="D152" t="n">
+        <v>1.255251</v>
+      </c>
+      <c r="E152" t="n">
+        <v>10.445713</v>
+      </c>
+      <c r="F152" t="n">
+        <v>1.120534</v>
+      </c>
+      <c r="G152" t="n">
+        <v>2.090288</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0.256717</v>
+      </c>
+      <c r="I152" t="n">
+        <v>1</v>
+      </c>
+      <c r="J152" t="n">
+        <v>0.6406182478852309</v>
+      </c>
+      <c r="L152" t="n">
+        <v>3.554499</v>
+      </c>
+      <c r="M152" t="n">
+        <v>0.6406182478852309</v>
+      </c>
+      <c r="N152" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>fake_hotels</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>0.04869</v>
+      </c>
+      <c r="D153" t="n">
+        <v>0.197307</v>
+      </c>
+      <c r="E153" t="n">
+        <v>0.656142</v>
+      </c>
+      <c r="F153" t="n">
+        <v>0.109601</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0.038064</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0.245721</v>
+      </c>
+      <c r="I153" t="n">
+        <v>0.8902819993245524</v>
+      </c>
+      <c r="J153" t="n">
+        <v>0.505340028590322</v>
+      </c>
+      <c r="L153" t="n">
+        <v>0.432678</v>
+      </c>
+      <c r="M153" t="n">
+        <v>0.505340028590322</v>
+      </c>
+      <c r="N153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>fake_hotels_extended</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>0.069746</v>
+      </c>
+      <c r="D154" t="n">
+        <v>5.417326</v>
+      </c>
+      <c r="E154" t="n">
+        <v>624.732891</v>
+      </c>
+      <c r="F154" t="n">
+        <v>2.010076</v>
+      </c>
+      <c r="G154" t="n">
+        <v>10.65305</v>
+      </c>
+      <c r="H154" t="n">
+        <v>0.20154</v>
+      </c>
+      <c r="I154" t="n">
+        <v>1</v>
+      </c>
+      <c r="J154" t="n">
+        <v>0.7082549399431972</v>
+      </c>
+      <c r="L154" t="n">
+        <v>16.373472</v>
+      </c>
+      <c r="M154" t="n">
+        <v>0.7082549399431972</v>
+      </c>
+      <c r="N154" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>fake_hotels_extended</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>0.069746</v>
+      </c>
+      <c r="D155" t="n">
+        <v>3.275692</v>
+      </c>
+      <c r="E155" t="n">
+        <v>618.6159270000001</v>
+      </c>
+      <c r="F155" t="n">
+        <v>1.346347</v>
+      </c>
+      <c r="G155" t="n">
+        <v>7.686998</v>
+      </c>
+      <c r="H155" t="n">
+        <v>0.199625</v>
+      </c>
+      <c r="I155" t="n">
+        <v>1</v>
+      </c>
+      <c r="J155" t="n">
+        <v>0.7325544631521609</v>
+      </c>
+      <c r="L155" t="n">
+        <v>11.281728</v>
+      </c>
+      <c r="M155" t="n">
+        <v>0.7325544631521609</v>
+      </c>
+      <c r="N155" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>fake_hotels_extended</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>0.069746</v>
+      </c>
+      <c r="D156" t="n">
+        <v>3.075671</v>
+      </c>
+      <c r="E156" t="n">
+        <v>11.612826</v>
+      </c>
+      <c r="F156" t="n">
+        <v>1.259458</v>
+      </c>
+      <c r="G156" t="n">
+        <v>1.858013</v>
+      </c>
+      <c r="H156" t="n">
+        <v>0.190148</v>
+      </c>
+      <c r="I156" t="n">
+        <v>1</v>
+      </c>
+      <c r="J156" t="n">
+        <v>0.7255465388740625</v>
+      </c>
+      <c r="L156" t="n">
+        <v>5.252722</v>
+      </c>
+      <c r="M156" t="n">
+        <v>0.7255465388740625</v>
+      </c>
+      <c r="N156" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>fake_hotels_extended</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>0.069746</v>
+      </c>
+      <c r="D157" t="n">
+        <v>0.303096</v>
+      </c>
+      <c r="E157" t="n">
+        <v>1.200568</v>
+      </c>
+      <c r="F157" t="n">
+        <v>0.157069</v>
+      </c>
+      <c r="G157" t="n">
+        <v>0.076778</v>
+      </c>
+      <c r="H157" t="n">
+        <v>0.184951</v>
+      </c>
+      <c r="I157" t="n">
+        <v>0.8816683552853766</v>
+      </c>
+      <c r="J157" t="n">
+        <v>0.5078313965291259</v>
+      </c>
+      <c r="L157" t="n">
+        <v>0.68297</v>
+      </c>
+      <c r="M157" t="n">
+        <v>0.5078313965291259</v>
+      </c>
+      <c r="N157" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>financial</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>85.38144</v>
+      </c>
+      <c r="D158" t="n">
+        <v>13531.845922</v>
+      </c>
+      <c r="F158" t="n">
+        <v>1058.068222</v>
+      </c>
+      <c r="G158" t="n">
+        <v>22361.096255</v>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>botocore.exceptions.SSLError: SSL validation failed for https://sdgym-benchmark.s3.amazonaws.com/Benchmarks/multi_table/SDGym_results_03_01_2026/financial_03_01_2026/HMASynthesizer%281%29/HMASynthesizer%281%29.pkl EOF occurred in violation of protocol (_ssl.c:2426)</t>
+        </is>
+      </c>
+      <c r="L158" t="n">
+        <v>35900.604116</v>
+      </c>
+      <c r="M158" t="n">
+        <v>0.5366362686210207</v>
+      </c>
+      <c r="N158" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>financial</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>85.38144</v>
+      </c>
+      <c r="D159" t="n">
+        <v>114.119245</v>
+      </c>
+      <c r="E159" t="n">
+        <v>1177.069269</v>
+      </c>
+      <c r="F159" t="n">
+        <v>25.339753</v>
+      </c>
+      <c r="G159" t="n">
+        <v>346.07432</v>
+      </c>
+      <c r="H159" t="n">
+        <v>9.316254000000001</v>
+      </c>
+      <c r="I159" t="n">
+        <v>1</v>
+      </c>
+      <c r="J159" t="n">
+        <v>0.7362523817467309</v>
+      </c>
+      <c r="L159" t="n">
+        <v>461.745752</v>
+      </c>
+      <c r="M159" t="n">
+        <v>0.7362523817467309</v>
+      </c>
+      <c r="N159" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>financial</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>85.38144</v>
+      </c>
+      <c r="D160" t="n">
+        <v>91.136011</v>
+      </c>
+      <c r="E160" t="n">
+        <v>914.284565</v>
+      </c>
+      <c r="F160" t="n">
+        <v>3.294061</v>
+      </c>
+      <c r="G160" t="n">
+        <v>355.97868</v>
+      </c>
+      <c r="H160" t="n">
+        <v>9.213982</v>
+      </c>
+      <c r="I160" t="n">
+        <v>1</v>
+      </c>
+      <c r="J160" t="n">
+        <v>0.731595063328388</v>
+      </c>
+      <c r="L160" t="n">
+        <v>448.666878</v>
+      </c>
+      <c r="M160" t="n">
+        <v>0.731595063328388</v>
+      </c>
+      <c r="N160" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>financial</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>85.38144</v>
+      </c>
+      <c r="D161" t="n">
+        <v>4.586851</v>
+      </c>
+      <c r="E161" t="n">
+        <v>492.459484</v>
+      </c>
+      <c r="F161" t="n">
+        <v>75.373344</v>
+      </c>
+      <c r="G161" t="n">
+        <v>3.075088</v>
+      </c>
+      <c r="H161" t="n">
+        <v>124.086843</v>
+      </c>
+      <c r="I161" t="n">
+        <v>0.8581208629120214</v>
+      </c>
+      <c r="J161" t="n">
+        <v>0.5366362686210207</v>
+      </c>
+      <c r="L161" t="n">
+        <v>12.24879</v>
+      </c>
+      <c r="M161" t="n">
+        <v>0.5366362686210207</v>
+      </c>
+      <c r="N161" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>ftp</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>4.683752</v>
+      </c>
+      <c r="D162" t="n">
+        <v>3536.454408</v>
+      </c>
+      <c r="E162" t="n">
+        <v>263.258753</v>
+      </c>
+      <c r="F162" t="n">
+        <v>4.132399</v>
+      </c>
+      <c r="G162" t="n">
+        <v>8645.306463000001</v>
+      </c>
+      <c r="H162" t="n">
+        <v>19.283839</v>
+      </c>
+      <c r="I162" t="n">
+        <v>1</v>
+      </c>
+      <c r="J162" t="n">
+        <v>0.6626514386204682</v>
+      </c>
+      <c r="L162" t="n">
+        <v>12181.907636</v>
+      </c>
+      <c r="M162" t="n">
+        <v>0.6626514386204682</v>
+      </c>
+      <c r="N162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>ftp</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>4.683752</v>
+      </c>
+      <c r="D163" t="n">
+        <v>11.439709</v>
+      </c>
+      <c r="E163" t="n">
+        <v>71.95410699999999</v>
+      </c>
+      <c r="F163" t="n">
+        <v>5.727733</v>
+      </c>
+      <c r="G163" t="n">
+        <v>19.339197</v>
+      </c>
+      <c r="H163" t="n">
+        <v>20.296233</v>
+      </c>
+      <c r="I163" t="n">
+        <v>1</v>
+      </c>
+      <c r="J163" t="n">
+        <v>0.6847955513140123</v>
+      </c>
+      <c r="L163" t="n">
+        <v>30.937514</v>
+      </c>
+      <c r="M163" t="n">
+        <v>0.6847955513140123</v>
+      </c>
+      <c r="N163" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>ftp</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>4.683752</v>
+      </c>
+      <c r="D164" t="n">
+        <v>7.529576</v>
+      </c>
+      <c r="E164" t="n">
+        <v>56.531641</v>
+      </c>
+      <c r="F164" t="n">
+        <v>4.445973</v>
+      </c>
+      <c r="G164" t="n">
+        <v>18.35007</v>
+      </c>
+      <c r="H164" t="n">
+        <v>20.320359</v>
+      </c>
+      <c r="I164" t="n">
+        <v>1</v>
+      </c>
+      <c r="J164" t="n">
+        <v>0.6655956310163569</v>
+      </c>
+      <c r="L164" t="n">
+        <v>26.038254</v>
+      </c>
+      <c r="M164" t="n">
+        <v>0.6655956310163569</v>
+      </c>
+      <c r="N164" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>ftp</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>4.683752</v>
+      </c>
+      <c r="D165" t="n">
+        <v>0.146765</v>
+      </c>
+      <c r="E165" t="n">
+        <v>25.988538</v>
+      </c>
+      <c r="F165" t="n">
+        <v>4.989718</v>
+      </c>
+      <c r="G165" t="n">
+        <v>0.067479</v>
+      </c>
+      <c r="H165" t="n">
+        <v>20.950788</v>
+      </c>
+      <c r="I165" t="n">
+        <v>0.8964442025570712</v>
+      </c>
+      <c r="J165" t="n">
+        <v>0.4180069556815814</v>
+      </c>
+      <c r="L165" t="n">
+        <v>0.361009</v>
+      </c>
+      <c r="M165" t="n">
+        <v>0.4180069556815814</v>
+      </c>
+      <c r="N165" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>genes</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>0.363488</v>
+      </c>
+      <c r="D166" t="n">
+        <v>203.792546</v>
+      </c>
+      <c r="E166" t="n">
+        <v>35.136927</v>
+      </c>
+      <c r="F166" t="n">
+        <v>2.34533</v>
+      </c>
+      <c r="G166" t="n">
+        <v>403.335577</v>
+      </c>
+      <c r="H166" t="n">
+        <v>0.346648</v>
+      </c>
+      <c r="I166" t="n">
+        <v>1</v>
+      </c>
+      <c r="J166" t="n">
+        <v>0.745650091874585</v>
+      </c>
+      <c r="L166" t="n">
+        <v>607.229143</v>
+      </c>
+      <c r="M166" t="n">
+        <v>0.745650091874585</v>
+      </c>
+      <c r="N166" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>genes</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>0.363488</v>
+      </c>
+      <c r="D167" t="n">
+        <v>2.624422</v>
+      </c>
+      <c r="E167" t="n">
+        <v>14.515945</v>
+      </c>
+      <c r="F167" t="n">
+        <v>1.595508</v>
+      </c>
+      <c r="G167" t="n">
+        <v>0.460921</v>
+      </c>
+      <c r="H167" t="n">
+        <v>0.353382</v>
+      </c>
+      <c r="I167" t="n">
+        <v>1</v>
+      </c>
+      <c r="J167" t="n">
+        <v>0.7882978843652539</v>
+      </c>
+      <c r="L167" t="n">
+        <v>3.189149</v>
+      </c>
+      <c r="M167" t="n">
+        <v>0.7882978843652539</v>
+      </c>
+      <c r="N167" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>genes</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>0.363488</v>
+      </c>
+      <c r="D168" t="n">
+        <v>2.329259</v>
+      </c>
+      <c r="E168" t="n">
+        <v>11.060843</v>
+      </c>
+      <c r="F168" t="n">
+        <v>1.386087</v>
+      </c>
+      <c r="G168" t="n">
+        <v>0.351901</v>
+      </c>
+      <c r="H168" t="n">
+        <v>0.348253</v>
+      </c>
+      <c r="I168" t="n">
+        <v>1</v>
+      </c>
+      <c r="J168" t="n">
+        <v>0.7656682802657299</v>
+      </c>
+      <c r="L168" t="n">
+        <v>2.784966</v>
+      </c>
+      <c r="M168" t="n">
+        <v>0.7656682802657299</v>
+      </c>
+      <c r="N168" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>genes</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>0.363488</v>
+      </c>
+      <c r="D169" t="n">
+        <v>0.10102</v>
+      </c>
+      <c r="E169" t="n">
+        <v>1.781675</v>
+      </c>
+      <c r="F169" t="n">
+        <v>0.291275</v>
+      </c>
+      <c r="G169" t="n">
+        <v>0.026764</v>
+      </c>
+      <c r="H169" t="n">
+        <v>0.340124</v>
+      </c>
+      <c r="I169" t="n">
+        <v>0.9136714863244164</v>
+      </c>
+      <c r="J169" t="n">
+        <v>0.414647769111359</v>
+      </c>
+      <c r="L169" t="n">
+        <v>0.228804</v>
+      </c>
+      <c r="M169" t="n">
+        <v>0.414647769111359</v>
+      </c>
+      <c r="N169" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>got_families</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D170" t="n">
+        <v>2.476753</v>
+      </c>
+      <c r="E170" t="n">
+        <v>19.948852</v>
+      </c>
+      <c r="F170" t="n">
+        <v>1.479158</v>
+      </c>
+      <c r="G170" t="n">
+        <v>1.597224</v>
+      </c>
+      <c r="H170" t="n">
+        <v>0.107907</v>
+      </c>
+      <c r="I170" t="n">
+        <v>1</v>
+      </c>
+      <c r="J170" t="n">
+        <v>0.3821428571428571</v>
+      </c>
+      <c r="L170" t="n">
+        <v>4.139834</v>
+      </c>
+      <c r="M170" t="n">
+        <v>0.3821428571428571</v>
+      </c>
+      <c r="N170" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>got_families</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D171" t="n">
+        <v>1.485716</v>
+      </c>
+      <c r="E171" t="n">
+        <v>13.375204</v>
+      </c>
+      <c r="F171" t="n">
+        <v>1.398049</v>
+      </c>
+      <c r="G171" t="n">
+        <v>0.228693</v>
+      </c>
+      <c r="H171" t="n">
+        <v>0.107395</v>
+      </c>
+      <c r="I171" t="n">
+        <v>1</v>
+      </c>
+      <c r="J171" t="n">
+        <v>0.4270833333333333</v>
+      </c>
+      <c r="L171" t="n">
+        <v>1.784591</v>
+      </c>
+      <c r="M171" t="n">
+        <v>0.4270833333333333</v>
+      </c>
+      <c r="N171" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>got_families</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D172" t="n">
+        <v>1.00451</v>
+      </c>
+      <c r="E172" t="n">
+        <v>12.758399</v>
+      </c>
+      <c r="F172" t="n">
+        <v>1.282768</v>
+      </c>
+      <c r="G172" t="n">
+        <v>0.137277</v>
+      </c>
+      <c r="H172" t="n">
+        <v>0.103414</v>
+      </c>
+      <c r="I172" t="n">
+        <v>1</v>
+      </c>
+      <c r="J172" t="n">
+        <v>0.4217261904761905</v>
+      </c>
+      <c r="L172" t="n">
+        <v>1.211969</v>
+      </c>
+      <c r="M172" t="n">
+        <v>0.4217261904761905</v>
+      </c>
+      <c r="N172" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>got_families</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D173" t="n">
+        <v>0.065857</v>
+      </c>
+      <c r="E173" t="n">
+        <v>0.073168</v>
+      </c>
+      <c r="F173" t="n">
+        <v>0.002784</v>
+      </c>
+      <c r="G173" t="n">
+        <v>0.009575999999999999</v>
+      </c>
+      <c r="H173" t="n">
+        <v>0.103739</v>
+      </c>
+      <c r="I173" t="n">
+        <v>0.8694727891156463</v>
+      </c>
+      <c r="J173" t="n">
+        <v>0.4701190476190476</v>
+      </c>
+      <c r="L173" t="n">
+        <v>0.14129</v>
+      </c>
+      <c r="M173" t="n">
+        <v>0.4701190476190476</v>
+      </c>
+      <c r="N173" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>imdb_MovieLens</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>39.205576</v>
+      </c>
+      <c r="D174" t="n">
+        <v>28567.391282</v>
+      </c>
+      <c r="E174" t="n">
+        <v>61357.484911</v>
+      </c>
+      <c r="F174" t="n">
+        <v>2.884023</v>
+      </c>
+      <c r="G174" t="n">
+        <v>46584.828883</v>
+      </c>
+      <c r="H174" t="n">
+        <v>3.563418</v>
+      </c>
+      <c r="I174" t="n">
+        <v>1</v>
+      </c>
+      <c r="J174" t="n">
+        <v>0.8672759103408504</v>
+      </c>
+      <c r="L174" t="n">
+        <v>75152.86644500001</v>
+      </c>
+      <c r="M174" t="n">
+        <v>0.8672759103408504</v>
+      </c>
+      <c r="N174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>imdb_MovieLens</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>39.205576</v>
+      </c>
+      <c r="D175" t="n">
+        <v>47.092746</v>
+      </c>
+      <c r="E175" t="n">
+        <v>555.012896</v>
+      </c>
+      <c r="F175" t="n">
+        <v>32.827998</v>
+      </c>
+      <c r="G175" t="n">
+        <v>26.581898</v>
+      </c>
+      <c r="H175" t="n">
+        <v>3.363031</v>
+      </c>
+      <c r="I175" t="n">
+        <v>1</v>
+      </c>
+      <c r="J175" t="n">
+        <v>0.9046789868376476</v>
+      </c>
+      <c r="L175" t="n">
+        <v>74.250244</v>
+      </c>
+      <c r="M175" t="n">
+        <v>0.9046789868376476</v>
+      </c>
+      <c r="N175" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>imdb_MovieLens</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>39.205576</v>
+      </c>
+      <c r="D176" t="n">
+        <v>11.412932</v>
+      </c>
+      <c r="E176" t="n">
+        <v>479.364225</v>
+      </c>
+      <c r="F176" t="n">
+        <v>2.601364</v>
+      </c>
+      <c r="G176" t="n">
+        <v>23.947807</v>
+      </c>
+      <c r="H176" t="n">
+        <v>3.291578</v>
+      </c>
+      <c r="I176" t="n">
+        <v>1</v>
+      </c>
+      <c r="J176" t="n">
+        <v>0.8760835779838435</v>
+      </c>
+      <c r="L176" t="n">
+        <v>35.936339</v>
+      </c>
+      <c r="M176" t="n">
+        <v>0.8760835779838435</v>
+      </c>
+      <c r="N176" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>imdb_MovieLens</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>39.205576</v>
+      </c>
+      <c r="D177" t="n">
+        <v>0.64628</v>
+      </c>
+      <c r="E177" t="n">
+        <v>185.985054</v>
+      </c>
+      <c r="F177" t="n">
+        <v>46.691893</v>
+      </c>
+      <c r="G177" t="n">
+        <v>0.411004</v>
+      </c>
+      <c r="H177" t="n">
+        <v>3.347955</v>
+      </c>
+      <c r="I177" t="n">
+        <v>0.8014452358295768</v>
+      </c>
+      <c r="J177" t="n">
+        <v>0.4216049520309001</v>
+      </c>
+      <c r="L177" t="n">
+        <v>1.703564</v>
+      </c>
+      <c r="M177" t="n">
+        <v>0.4216049520309001</v>
+      </c>
+      <c r="N177" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>imdb_ijs</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Synthesizer Timeout</t>
+        </is>
+      </c>
+      <c r="L178" t="n">
+        <v>345868.7219229999</v>
+      </c>
+      <c r="M178" t="n">
+        <v>0.3341177384614725</v>
+      </c>
+      <c r="N178" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>imdb_ijs</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>173.901672</v>
+      </c>
+      <c r="D179" t="n">
+        <v>356.983084</v>
+      </c>
+      <c r="E179" t="n">
+        <v>3409.710586</v>
+      </c>
+      <c r="F179" t="n">
+        <v>371.651719</v>
+      </c>
+      <c r="G179" t="n">
+        <v>158.603168</v>
+      </c>
+      <c r="H179" t="n">
+        <v>22083.481555</v>
+      </c>
+      <c r="I179" t="n">
+        <v>1</v>
+      </c>
+      <c r="J179" t="n">
+        <v>0.490526972483848</v>
+      </c>
+      <c r="L179" t="n">
+        <v>520.2596040000001</v>
+      </c>
+      <c r="M179" t="n">
+        <v>0.490526972483848</v>
+      </c>
+      <c r="N179" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>imdb_ijs</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>173.901672</v>
+      </c>
+      <c r="D180" t="n">
+        <v>212.682511</v>
+      </c>
+      <c r="E180" t="n">
+        <v>2019.100192</v>
+      </c>
+      <c r="F180" t="n">
+        <v>202.654298</v>
+      </c>
+      <c r="G180" t="n">
+        <v>149.649749</v>
+      </c>
+      <c r="H180" t="n">
+        <v>22220.580829</v>
+      </c>
+      <c r="I180" t="n">
+        <v>1</v>
+      </c>
+      <c r="J180" t="n">
+        <v>0.5012462475010605</v>
+      </c>
+      <c r="L180" t="n">
+        <v>367.005612</v>
+      </c>
+      <c r="M180" t="n">
+        <v>0.5012462475010605</v>
+      </c>
+      <c r="N180" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>imdb_ijs</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>173.901672</v>
+      </c>
+      <c r="D181" t="n">
+        <v>124.029664</v>
+      </c>
+      <c r="E181" t="n">
+        <v>4474.696379</v>
+      </c>
+      <c r="F181" t="n">
+        <v>249.31019</v>
+      </c>
+      <c r="G181" t="n">
+        <v>144.692259</v>
+      </c>
+      <c r="H181" t="n">
+        <v>74174.03787999999</v>
+      </c>
+      <c r="I181" t="n">
+        <v>0.8909384233685133</v>
+      </c>
+      <c r="J181" t="n">
+        <v>0.3341177384614725</v>
+      </c>
+      <c r="L181" t="n">
+        <v>392.751587</v>
+      </c>
+      <c r="M181" t="n">
+        <v>0.3341177384614725</v>
+      </c>
+      <c r="N181" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>imdb_small</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>0.153088</v>
+      </c>
+      <c r="D182" t="n">
+        <v>221.125037</v>
+      </c>
+      <c r="E182" t="n">
+        <v>73.117512</v>
+      </c>
+      <c r="F182" t="n">
+        <v>3.279481</v>
+      </c>
+      <c r="G182" t="n">
+        <v>242.480315</v>
+      </c>
+      <c r="H182" t="n">
+        <v>0.603954</v>
+      </c>
+      <c r="I182" t="n">
+        <v>1</v>
+      </c>
+      <c r="J182" t="n">
+        <v>0.5091571284506169</v>
+      </c>
+      <c r="L182" t="n">
+        <v>463.845359</v>
+      </c>
+      <c r="M182" t="n">
+        <v>0.5091571284506169</v>
+      </c>
+      <c r="N182" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>imdb_small</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>0.153088</v>
+      </c>
+      <c r="D183" t="n">
+        <v>3.629567</v>
+      </c>
+      <c r="E183" t="n">
+        <v>39.76545</v>
+      </c>
+      <c r="F183" t="n">
+        <v>3.4405</v>
+      </c>
+      <c r="G183" t="n">
+        <v>0.79897</v>
+      </c>
+      <c r="H183" t="n">
+        <v>0.60144</v>
+      </c>
+      <c r="I183" t="n">
+        <v>1</v>
+      </c>
+      <c r="J183" t="n">
+        <v>0.5924944469137565</v>
+      </c>
+      <c r="L183" t="n">
+        <v>4.694137</v>
+      </c>
+      <c r="M183" t="n">
+        <v>0.5924944469137565</v>
+      </c>
+      <c r="N183" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>imdb_small</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>0.153088</v>
+      </c>
+      <c r="D184" t="n">
+        <v>3.422141</v>
+      </c>
+      <c r="E184" t="n">
+        <v>33.052516</v>
+      </c>
+      <c r="F184" t="n">
+        <v>3.005959</v>
+      </c>
+      <c r="G184" t="n">
+        <v>0.580485</v>
+      </c>
+      <c r="H184" t="n">
+        <v>0.594784</v>
+      </c>
+      <c r="I184" t="n">
+        <v>1</v>
+      </c>
+      <c r="J184" t="n">
+        <v>0.5923823181302825</v>
+      </c>
+      <c r="L184" t="n">
+        <v>4.268226</v>
+      </c>
+      <c r="M184" t="n">
+        <v>0.5923823181302825</v>
+      </c>
+      <c r="N184" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>imdb_small</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>0.153088</v>
+      </c>
+      <c r="D185" t="n">
+        <v>0.240007</v>
+      </c>
+      <c r="E185" t="n">
+        <v>1.330927</v>
+      </c>
+      <c r="F185" t="n">
+        <v>0.238822</v>
+      </c>
+      <c r="G185" t="n">
+        <v>0.045204</v>
+      </c>
+      <c r="H185" t="n">
+        <v>0.548223</v>
+      </c>
+      <c r="I185" t="n">
+        <v>0.674270279754707</v>
+      </c>
+      <c r="J185" t="n">
+        <v>0.2860989823024679</v>
+      </c>
+      <c r="L185" t="n">
+        <v>0.525218</v>
+      </c>
+      <c r="M185" t="n">
+        <v>0.2860989823024679</v>
+      </c>
+      <c r="N185" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>legalActs</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Synthesizer Timeout</t>
+        </is>
+      </c>
+      <c r="L186" t="n">
+        <v>346218.271668</v>
+      </c>
+      <c r="M186" t="n">
+        <v>0.3429179369479918</v>
+      </c>
+      <c r="N186" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>legalActs</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>130.303928</v>
+      </c>
+      <c r="D187" t="n">
+        <v>257.42402</v>
+      </c>
+      <c r="E187" t="n">
+        <v>1906.171839</v>
+      </c>
+      <c r="F187" t="n">
+        <v>134.175777</v>
+      </c>
+      <c r="G187" t="n">
+        <v>66.355323</v>
+      </c>
+      <c r="H187" t="n">
+        <v>4943.260563999999</v>
+      </c>
+      <c r="I187" t="n">
+        <v>1</v>
+      </c>
+      <c r="J187" t="n">
+        <v>0.6596943553437395</v>
+      </c>
+      <c r="L187" t="n">
+        <v>327.257397</v>
+      </c>
+      <c r="M187" t="n">
+        <v>0.6596943553437395</v>
+      </c>
+      <c r="N187" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>legalActs</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>130.303928</v>
+      </c>
+      <c r="D188" t="n">
+        <v>195.917513</v>
+      </c>
+      <c r="E188" t="n">
+        <v>1783.958938</v>
+      </c>
+      <c r="F188" t="n">
+        <v>95.20282899999999</v>
+      </c>
+      <c r="G188" t="n">
+        <v>65.203093</v>
+      </c>
+      <c r="H188" t="n">
+        <v>4933.93951</v>
+      </c>
+      <c r="I188" t="n">
+        <v>1</v>
+      </c>
+      <c r="J188" t="n">
+        <v>0.6578342285278733</v>
+      </c>
+      <c r="L188" t="n">
+        <v>264.59866</v>
+      </c>
+      <c r="M188" t="n">
+        <v>0.6578342285278733</v>
+      </c>
+      <c r="N188" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>legalActs</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>130.303928</v>
+      </c>
+      <c r="D189" t="n">
+        <v>329.455349</v>
+      </c>
+      <c r="E189" t="n">
+        <v>2121.90865</v>
+      </c>
+      <c r="F189" t="n">
+        <v>146.609887</v>
+      </c>
+      <c r="G189" t="n">
+        <v>288.816319</v>
+      </c>
+      <c r="H189" t="n">
+        <v>21277.58196</v>
+      </c>
+      <c r="I189" t="n">
+        <v>0.8499113625917425</v>
+      </c>
+      <c r="J189" t="n">
+        <v>0.3429179369479918</v>
+      </c>
+      <c r="L189" t="n">
+        <v>947.727017</v>
+      </c>
+      <c r="M189" t="n">
+        <v>0.3429179369479918</v>
+      </c>
+      <c r="N189" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>multi_table_ID_demo_dataset</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>0.693312</v>
+      </c>
+      <c r="D190" t="n">
+        <v>167.49149</v>
+      </c>
+      <c r="E190" t="n">
+        <v>199.823649</v>
+      </c>
+      <c r="F190" t="n">
+        <v>8.144629</v>
+      </c>
+      <c r="G190" t="n">
+        <v>206.962141</v>
+      </c>
+      <c r="H190" t="n">
+        <v>0.1938389999999999</v>
+      </c>
+      <c r="I190" t="n">
+        <v>1</v>
+      </c>
+      <c r="J190" t="n">
+        <v>0.6561015873015873</v>
+      </c>
+      <c r="L190" t="n">
+        <v>374.687414</v>
+      </c>
+      <c r="M190" t="n">
+        <v>0.6561015873015873</v>
+      </c>
+      <c r="N190" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>multi_table_ID_demo_dataset</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>0.693312</v>
+      </c>
+      <c r="D191" t="n">
+        <v>3.933926</v>
+      </c>
+      <c r="E191" t="n">
+        <v>37.576973</v>
+      </c>
+      <c r="F191" t="n">
+        <v>4.040184</v>
+      </c>
+      <c r="G191" t="n">
+        <v>0.989296</v>
+      </c>
+      <c r="H191" t="n">
+        <v>0.191995</v>
+      </c>
+      <c r="I191" t="n">
+        <v>1</v>
+      </c>
+      <c r="J191" t="n">
+        <v>0.684631746031746</v>
+      </c>
+      <c r="L191" t="n">
+        <v>5.197502</v>
+      </c>
+      <c r="M191" t="n">
+        <v>0.684631746031746</v>
+      </c>
+      <c r="N191" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>multi_table_ID_demo_dataset</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>0.693312</v>
+      </c>
+      <c r="D192" t="n">
+        <v>3.534542</v>
+      </c>
+      <c r="E192" t="n">
+        <v>36.061197</v>
+      </c>
+      <c r="F192" t="n">
+        <v>3.630031</v>
+      </c>
+      <c r="G192" t="n">
+        <v>0.799741</v>
+      </c>
+      <c r="H192" t="n">
+        <v>0.196877</v>
+      </c>
+      <c r="I192" t="n">
+        <v>1</v>
+      </c>
+      <c r="J192" t="n">
+        <v>0.6962793650793651</v>
+      </c>
+      <c r="L192" t="n">
+        <v>4.608563</v>
+      </c>
+      <c r="M192" t="n">
+        <v>0.6962793650793651</v>
+      </c>
+      <c r="N192" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>multi_table_ID_demo_dataset</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>0.693312</v>
+      </c>
+      <c r="D193" t="n">
+        <v>0.233783</v>
+      </c>
+      <c r="E193" t="n">
+        <v>3.35943</v>
+      </c>
+      <c r="F193" t="n">
+        <v>0.786745</v>
+      </c>
+      <c r="G193" t="n">
+        <v>0.043778</v>
+      </c>
+      <c r="H193" t="n">
+        <v>0.184565</v>
+      </c>
+      <c r="I193" t="n">
+        <v>0.6558186868686869</v>
+      </c>
+      <c r="J193" t="n">
+        <v>0.3607619047619048</v>
+      </c>
+      <c r="L193" t="n">
+        <v>0.511344</v>
+      </c>
+      <c r="M193" t="n">
+        <v>0.3607619047619048</v>
+      </c>
+      <c r="N193" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>mutagenesis</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>0.372904</v>
+      </c>
+      <c r="D194" t="n">
+        <v>917.048211</v>
+      </c>
+      <c r="E194" t="n">
+        <v>441.264412</v>
+      </c>
+      <c r="F194" t="n">
+        <v>2.580145</v>
+      </c>
+      <c r="G194" t="n">
+        <v>1326.196673</v>
+      </c>
+      <c r="H194" t="n">
+        <v>0.299755</v>
+      </c>
+      <c r="I194" t="n">
+        <v>1</v>
+      </c>
+      <c r="J194" t="n">
+        <v>0.6533609354277707</v>
+      </c>
+      <c r="L194" t="n">
+        <v>2243.388256</v>
+      </c>
+      <c r="M194" t="n">
+        <v>0.6533609354277707</v>
+      </c>
+      <c r="N194" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>mutagenesis</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>0.372904</v>
+      </c>
+      <c r="D195" t="n">
+        <v>2.233639</v>
+      </c>
+      <c r="E195" t="n">
+        <v>15.022513</v>
+      </c>
+      <c r="F195" t="n">
+        <v>1.712218</v>
+      </c>
+      <c r="G195" t="n">
+        <v>0.522848</v>
+      </c>
+      <c r="H195" t="n">
+        <v>0.303807</v>
+      </c>
+      <c r="I195" t="n">
+        <v>1</v>
+      </c>
+      <c r="J195" t="n">
+        <v>0.6759954291483063</v>
+      </c>
+      <c r="L195" t="n">
+        <v>2.9452</v>
+      </c>
+      <c r="M195" t="n">
+        <v>0.6759954291483063</v>
+      </c>
+      <c r="N195" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>mutagenesis</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>0.372904</v>
+      </c>
+      <c r="D196" t="n">
+        <v>1.788711</v>
+      </c>
+      <c r="E196" t="n">
+        <v>13.72749</v>
+      </c>
+      <c r="F196" t="n">
+        <v>1.340405</v>
+      </c>
+      <c r="G196" t="n">
+        <v>0.4049</v>
+      </c>
+      <c r="H196" t="n">
+        <v>0.328385</v>
+      </c>
+      <c r="I196" t="n">
+        <v>1</v>
+      </c>
+      <c r="J196" t="n">
+        <v>0.6586582763913214</v>
+      </c>
+      <c r="L196" t="n">
+        <v>2.382324</v>
+      </c>
+      <c r="M196" t="n">
+        <v>0.6586582763913214</v>
+      </c>
+      <c r="N196" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>mutagenesis</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>0.372904</v>
+      </c>
+      <c r="D197" t="n">
+        <v>0.143372</v>
+      </c>
+      <c r="E197" t="n">
+        <v>1.850421</v>
+      </c>
+      <c r="F197" t="n">
+        <v>0.429543</v>
+      </c>
+      <c r="G197" t="n">
+        <v>0.043757</v>
+      </c>
+      <c r="H197" t="n">
+        <v>0.305671</v>
+      </c>
+      <c r="I197" t="n">
+        <v>0.9061239526391888</v>
+      </c>
+      <c r="J197" t="n">
+        <v>0.5000038163252849</v>
+      </c>
+      <c r="L197" t="n">
+        <v>0.330501</v>
+      </c>
+      <c r="M197" t="n">
+        <v>0.5000038163252849</v>
+      </c>
+      <c r="N197" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>nations</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>0.452192</v>
+      </c>
+      <c r="D198" t="n">
+        <v>1924.419806</v>
+      </c>
+      <c r="E198" t="n">
+        <v>4971.422429</v>
+      </c>
+      <c r="F198" t="n">
+        <v>429.717353</v>
+      </c>
+      <c r="G198" t="n">
+        <v>203.735982</v>
+      </c>
+      <c r="H198" t="n">
+        <v>48.180683</v>
+      </c>
+      <c r="I198" t="n">
+        <v>1</v>
+      </c>
+      <c r="J198" t="n">
+        <v>0.786758130153503</v>
+      </c>
+      <c r="L198" t="n">
+        <v>2130.570804</v>
+      </c>
+      <c r="M198" t="n">
+        <v>0.786758130153503</v>
+      </c>
+      <c r="N198" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>nations</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>0.452192</v>
+      </c>
+      <c r="D199" t="n">
+        <v>7.684181</v>
+      </c>
+      <c r="E199" t="n">
+        <v>21.19483</v>
+      </c>
+      <c r="F199" t="n">
+        <v>3.132572</v>
+      </c>
+      <c r="G199" t="n">
+        <v>2.210886</v>
+      </c>
+      <c r="H199" t="n">
+        <v>24.644102</v>
+      </c>
+      <c r="I199" t="n">
+        <v>1</v>
+      </c>
+      <c r="J199" t="n">
+        <v>0.7818016747186043</v>
+      </c>
+      <c r="L199" t="n">
+        <v>11.487736</v>
+      </c>
+      <c r="M199" t="n">
+        <v>0.7818016747186043</v>
+      </c>
+      <c r="N199" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>nations</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>0.452192</v>
+      </c>
+      <c r="D200" t="n">
+        <v>5.796435</v>
+      </c>
+      <c r="E200" t="n">
+        <v>18.077915</v>
+      </c>
+      <c r="F200" t="n">
+        <v>2.669613</v>
+      </c>
+      <c r="G200" t="n">
+        <v>1.894823</v>
+      </c>
+      <c r="H200" t="n">
+        <v>24.885941</v>
+      </c>
+      <c r="I200" t="n">
+        <v>1</v>
+      </c>
+      <c r="J200" t="n">
+        <v>0.7935149599929394</v>
+      </c>
+      <c r="L200" t="n">
+        <v>9.283927</v>
+      </c>
+      <c r="M200" t="n">
+        <v>0.7935149599929394</v>
+      </c>
+      <c r="N200" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>nations</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>0.452192</v>
+      </c>
+      <c r="D201" t="n">
+        <v>2.415016</v>
+      </c>
+      <c r="E201" t="n">
+        <v>47.03017</v>
+      </c>
+      <c r="F201" t="n">
+        <v>0.918723</v>
+      </c>
+      <c r="G201" t="n">
+        <v>0.993561</v>
+      </c>
+      <c r="H201" t="n">
+        <v>51.440956</v>
+      </c>
+      <c r="I201" t="n">
+        <v>0.7904291829674484</v>
+      </c>
+      <c r="J201" t="n">
+        <v>0.5183164798121153</v>
+      </c>
+      <c r="L201" t="n">
+        <v>5.823593</v>
+      </c>
+      <c r="M201" t="n">
+        <v>0.5183164798121153</v>
+      </c>
+      <c r="N201" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>restbase</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>0.693264</v>
+      </c>
+      <c r="D202" t="n">
+        <v>1124.335172</v>
+      </c>
+      <c r="E202" t="n">
+        <v>74.944818</v>
+      </c>
+      <c r="F202" t="n">
+        <v>4.118746</v>
+      </c>
+      <c r="G202" t="n">
+        <v>1438.487223</v>
+      </c>
+      <c r="H202" t="n">
+        <v>2.713649</v>
+      </c>
+      <c r="I202" t="n">
+        <v>1</v>
+      </c>
+      <c r="J202" t="n">
+        <v>0.467863610527153</v>
+      </c>
+      <c r="L202" t="n">
+        <v>2562.944189</v>
+      </c>
+      <c r="M202" t="n">
+        <v>0.467863610527153</v>
+      </c>
+      <c r="N202" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>restbase</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>0.693264</v>
+      </c>
+      <c r="D203" t="n">
+        <v>3.130598</v>
+      </c>
+      <c r="E203" t="n">
+        <v>31.295469</v>
+      </c>
+      <c r="F203" t="n">
+        <v>2.895851</v>
+      </c>
+      <c r="G203" t="n">
+        <v>0.856995</v>
+      </c>
+      <c r="H203" t="n">
+        <v>2.751141</v>
+      </c>
+      <c r="I203" t="n">
+        <v>1</v>
+      </c>
+      <c r="J203" t="n">
+        <v>0.5515730437325312</v>
+      </c>
+      <c r="L203" t="n">
+        <v>4.149985</v>
+      </c>
+      <c r="M203" t="n">
+        <v>0.5515730437325312</v>
+      </c>
+      <c r="N203" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>restbase</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>0.693264</v>
+      </c>
+      <c r="D204" t="n">
+        <v>2.232681</v>
+      </c>
+      <c r="E204" t="n">
+        <v>30.92105</v>
+      </c>
+      <c r="F204" t="n">
+        <v>2.516334</v>
+      </c>
+      <c r="G204" t="n">
+        <v>0.7310179999999999</v>
+      </c>
+      <c r="H204" t="n">
+        <v>2.79372</v>
+      </c>
+      <c r="I204" t="n">
+        <v>1</v>
+      </c>
+      <c r="J204" t="n">
+        <v>0.5291285828812423</v>
+      </c>
+      <c r="L204" t="n">
+        <v>3.126091</v>
+      </c>
+      <c r="M204" t="n">
+        <v>0.5291285828812423</v>
+      </c>
+      <c r="N204" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>restbase</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>0.693264</v>
+      </c>
+      <c r="D205" t="n">
+        <v>0.121794</v>
+      </c>
+      <c r="E205" t="n">
+        <v>2.771542</v>
+      </c>
+      <c r="F205" t="n">
+        <v>0.746761</v>
+      </c>
+      <c r="G205" t="n">
+        <v>0.036729</v>
+      </c>
+      <c r="H205" t="n">
+        <v>2.85173</v>
+      </c>
+      <c r="I205" t="n">
+        <v>0.8946537480847768</v>
+      </c>
+      <c r="J205" t="n">
+        <v>0.2564426217372977</v>
+      </c>
+      <c r="L205" t="n">
+        <v>0.280317</v>
+      </c>
+      <c r="M205" t="n">
+        <v>0.2564426217372977</v>
+      </c>
+      <c r="N205" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>trains</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>0.005776</v>
+      </c>
+      <c r="D206" t="n">
+        <v>4.421982</v>
+      </c>
+      <c r="E206" t="n">
+        <v>19.459025</v>
+      </c>
+      <c r="F206" t="n">
+        <v>1.83393</v>
+      </c>
+      <c r="G206" t="n">
+        <v>4.690847</v>
+      </c>
+      <c r="H206" t="n">
+        <v>0.206565</v>
+      </c>
+      <c r="I206" t="n">
+        <v>1</v>
+      </c>
+      <c r="J206" t="n">
+        <v>0.747995522995523</v>
+      </c>
+      <c r="L206" t="n">
+        <v>9.182313000000001</v>
+      </c>
+      <c r="M206" t="n">
+        <v>0.747995522995523</v>
+      </c>
+      <c r="N206" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>trains</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>0.005776</v>
+      </c>
+      <c r="D207" t="n">
+        <v>1.34138</v>
+      </c>
+      <c r="E207" t="n">
+        <v>10.475943</v>
+      </c>
+      <c r="F207" t="n">
+        <v>1.153434</v>
+      </c>
+      <c r="G207" t="n">
+        <v>0.255761</v>
+      </c>
+      <c r="H207" t="n">
+        <v>0.214969</v>
+      </c>
+      <c r="I207" t="n">
+        <v>1</v>
+      </c>
+      <c r="J207" t="n">
+        <v>0.8848127798127798</v>
+      </c>
+      <c r="L207" t="n">
+        <v>1.671654</v>
+      </c>
+      <c r="M207" t="n">
+        <v>0.8848127798127798</v>
+      </c>
+      <c r="N207" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>trains</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>0.005776</v>
+      </c>
+      <c r="D208" t="n">
+        <v>1.094858</v>
+      </c>
+      <c r="E208" t="n">
+        <v>10.076497</v>
+      </c>
+      <c r="F208" t="n">
+        <v>1.086677</v>
+      </c>
+      <c r="G208" t="n">
+        <v>0.194729</v>
+      </c>
+      <c r="H208" t="n">
+        <v>0.213069</v>
+      </c>
+      <c r="I208" t="n">
+        <v>1</v>
+      </c>
+      <c r="J208" t="n">
+        <v>0.8320634920634921</v>
+      </c>
+      <c r="L208" t="n">
+        <v>1.3641</v>
+      </c>
+      <c r="M208" t="n">
+        <v>0.8320634920634921</v>
+      </c>
+      <c r="N208" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>trains</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>0.005776</v>
+      </c>
+      <c r="D209" t="n">
+        <v>0.069484</v>
+      </c>
+      <c r="E209" t="n">
+        <v>0.098661</v>
+      </c>
+      <c r="F209" t="n">
+        <v>0.005788</v>
+      </c>
+      <c r="G209" t="n">
+        <v>0.011782</v>
+      </c>
+      <c r="H209" t="n">
+        <v>0.204702</v>
+      </c>
+      <c r="I209" t="n">
+        <v>0.850242504409171</v>
+      </c>
+      <c r="J209" t="n">
+        <v>0.6038298738298739</v>
+      </c>
+      <c r="L209" t="n">
+        <v>0.15075</v>
+      </c>
+      <c r="M209" t="n">
+        <v>0.6038298738298739</v>
+      </c>
+      <c r="N209" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>0.006616</v>
+      </c>
+      <c r="D210" t="n">
+        <v>10.885008</v>
+      </c>
+      <c r="E210" t="n">
+        <v>31.739899</v>
+      </c>
+      <c r="F210" t="n">
+        <v>2.355725</v>
+      </c>
+      <c r="G210" t="n">
+        <v>11.456367</v>
+      </c>
+      <c r="H210" t="n">
+        <v>0.194404</v>
+      </c>
+      <c r="I210" t="n">
+        <v>1</v>
+      </c>
+      <c r="J210" t="n">
+        <v>0.8085585775228523</v>
+      </c>
+      <c r="L210" t="n">
+        <v>22.473634</v>
+      </c>
+      <c r="M210" t="n">
+        <v>0.8085585775228523</v>
+      </c>
+      <c r="N210" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>0.006616</v>
+      </c>
+      <c r="D211" t="n">
+        <v>2.583773</v>
+      </c>
+      <c r="E211" t="n">
+        <v>23.39528</v>
+      </c>
+      <c r="F211" t="n">
+        <v>2.178847</v>
+      </c>
+      <c r="G211" t="n">
+        <v>0.461824</v>
+      </c>
+      <c r="H211" t="n">
+        <v>0.203645</v>
+      </c>
+      <c r="I211" t="n">
+        <v>1</v>
+      </c>
+      <c r="J211" t="n">
+        <v>0.8037514583877495</v>
+      </c>
+      <c r="L211" t="n">
+        <v>3.162909</v>
+      </c>
+      <c r="M211" t="n">
+        <v>0.8037514583877495</v>
+      </c>
+      <c r="N211" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>0.006616</v>
+      </c>
+      <c r="D212" t="n">
+        <v>2.103323</v>
+      </c>
+      <c r="E212" t="n">
+        <v>22.931007</v>
+      </c>
+      <c r="F212" t="n">
+        <v>1.965285</v>
+      </c>
+      <c r="G212" t="n">
+        <v>0.280695</v>
+      </c>
+      <c r="H212" t="n">
+        <v>0.204544</v>
+      </c>
+      <c r="I212" t="n">
+        <v>1</v>
+      </c>
+      <c r="J212" t="n">
+        <v>0.7789171298591299</v>
+      </c>
+      <c r="L212" t="n">
+        <v>2.50133</v>
+      </c>
+      <c r="M212" t="n">
+        <v>0.7789171298591299</v>
+      </c>
+      <c r="N212" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>0.006616</v>
+      </c>
+      <c r="D213" t="n">
+        <v>0.132259</v>
+      </c>
+      <c r="E213" t="n">
+        <v>0.129564</v>
+      </c>
+      <c r="F213" t="n">
+        <v>0.008839</v>
+      </c>
+      <c r="G213" t="n">
+        <v>0.019354</v>
+      </c>
+      <c r="H213" t="n">
+        <v>0.193265</v>
+      </c>
+      <c r="I213" t="n">
+        <v>0.8048226756504788</v>
+      </c>
+      <c r="J213" t="n">
+        <v>0.6609110795643359</v>
+      </c>
+      <c r="L213" t="n">
+        <v>0.2838719999999999</v>
+      </c>
+      <c r="M213" t="n">
+        <v>0.6609110795643359</v>
+      </c>
+      <c r="N213" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>HMASynthesizer</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>world</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>0.231584</v>
+      </c>
+      <c r="D214" t="n">
+        <v>55.691263</v>
+      </c>
+      <c r="E214" t="n">
+        <v>26.409083</v>
+      </c>
+      <c r="F214" t="n">
+        <v>2.458059</v>
+      </c>
+      <c r="G214" t="n">
+        <v>74.738523</v>
+      </c>
+      <c r="H214" t="n">
+        <v>1.854095</v>
+      </c>
+      <c r="I214" t="n">
+        <v>1</v>
+      </c>
+      <c r="J214" t="n">
+        <v>0.5200317461990861</v>
+      </c>
+      <c r="L214" t="n">
+        <v>130.72244</v>
+      </c>
+      <c r="M214" t="n">
+        <v>0.5200317461990861</v>
+      </c>
+      <c r="N214" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>HSASynthesizer</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>world</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>0.231584</v>
+      </c>
+      <c r="D215" t="n">
+        <v>2.808676</v>
+      </c>
+      <c r="E215" t="n">
+        <v>20.945719</v>
+      </c>
+      <c r="F215" t="n">
+        <v>2.35301</v>
+      </c>
+      <c r="G215" t="n">
+        <v>0.696643</v>
+      </c>
+      <c r="H215" t="n">
+        <v>1.881471</v>
+      </c>
+      <c r="I215" t="n">
+        <v>1</v>
+      </c>
+      <c r="J215" t="n">
+        <v>0.4380996465757931</v>
+      </c>
+      <c r="L215" t="n">
+        <v>3.806215</v>
+      </c>
+      <c r="M215" t="n">
+        <v>0.4380996465757931</v>
+      </c>
+      <c r="N215" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>world</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>0.231584</v>
+      </c>
+      <c r="D216" t="n">
+        <v>2.694583</v>
+      </c>
+      <c r="E216" t="n">
+        <v>18.488773</v>
+      </c>
+      <c r="F216" t="n">
+        <v>2.127616</v>
+      </c>
+      <c r="G216" t="n">
+        <v>0.578678</v>
+      </c>
+      <c r="H216" t="n">
+        <v>1.893969</v>
+      </c>
+      <c r="I216" t="n">
+        <v>1</v>
+      </c>
+      <c r="J216" t="n">
+        <v>0.45612267695798</v>
+      </c>
+      <c r="L216" t="n">
+        <v>3.574157</v>
+      </c>
+      <c r="M216" t="n">
+        <v>0.45612267695798</v>
+      </c>
+      <c r="N216" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>MultiTableUniformSynthesizer</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>world</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>0.231584</v>
+      </c>
+      <c r="D217" t="n">
+        <v>0.292654</v>
+      </c>
+      <c r="E217" t="n">
+        <v>1.527882</v>
+      </c>
+      <c r="F217" t="n">
+        <v>0.317796</v>
+      </c>
+      <c r="G217" t="n">
+        <v>0.07632899999999999</v>
+      </c>
+      <c r="H217" t="n">
+        <v>1.874147</v>
+      </c>
+      <c r="I217" t="n">
+        <v>0.924395539379012</v>
+      </c>
+      <c r="J217" t="n">
+        <v>0.3165230151776433</v>
+      </c>
+      <c r="L217" t="n">
+        <v>0.661637</v>
+      </c>
+      <c r="M217" t="n">
+        <v>0.3165230151776433</v>
+      </c>
+      <c r="N217" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Synthesizer</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Aggregated_Time</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Quality_Score</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Log10 Aggregated_Time</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Pareto</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Marker</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MultiTableUniform</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2140.599166</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.522414699077867</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3.330535351884883</v>
+      </c>
+      <c r="E2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>#01E0C9</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>circle</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Independent</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>4007.726803</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.7558331557550066</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3.602898109068408</v>
+      </c>
+      <c r="E3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>#01E0C9</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>square</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>HSA</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>4994.72635</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.7673830533298976</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3.698511699180513</v>
+      </c>
+      <c r="E4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>#01E0C9</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>diamond</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>HMA</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2594514.797863</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.6829860537773095</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6.414056152044597</v>
+      </c>
+      <c r="E5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>#03AFF1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="n">
+        <v>1203.747371709796</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.3081614187368837</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3.080535351884883</v>
+      </c>
+      <c r="E6" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>#01E0C9</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
+        <v>4613772.244081069</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.125613872235522</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6.664056152044597</v>
+      </c>
+      <c r="E7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>#01E0C9</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10096,7 +19945,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10310,7 +20159,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11618,7 +21467,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/assets/[Multi-table]_SDGym_Runs.xlsx
+++ b/assets/[Multi-table]_SDGym_Runs.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -469,7 +469,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2" t="n">
         <v>8</v>
@@ -485,10 +485,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C3" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
@@ -497,16 +497,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>IndependentSynthesizer</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>52</v>
+      </c>
+      <c r="C4" t="n">
+        <v>50</v>
+      </c>
+      <c r="D4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>MultiTableUniformSynthesizer</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="n">
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
         <v>2</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -674,7 +690,7 @@
         <v>0.5954709920794259</v>
       </c>
       <c r="L3" t="n">
-        <v>419.2464230000001</v>
+        <v>608.771993</v>
       </c>
       <c r="M3" t="n">
         <v>0.5954709920794259</v>
@@ -719,13 +735,13 @@
         <v>0.592826439841007</v>
       </c>
       <c r="L4" t="n">
-        <v>384.877075</v>
+        <v>574.4026449999999</v>
       </c>
       <c r="M4" t="n">
         <v>0.592826439841007</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -854,7 +870,7 @@
         <v>0.7733684836818895</v>
       </c>
       <c r="L7" t="n">
-        <v>26.543476</v>
+        <v>66.897301</v>
       </c>
       <c r="M7" t="n">
         <v>0.7733684836818895</v>
@@ -899,13 +915,13 @@
         <v>0.7650116192280561</v>
       </c>
       <c r="L8" t="n">
-        <v>25.591657</v>
+        <v>65.945482</v>
       </c>
       <c r="M8" t="n">
         <v>0.7650116192280561</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -970,7 +986,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.785349</v>
+        <v>1.081524</v>
       </c>
       <c r="M10" t="n">
         <v>0.4225208651670076</v>
@@ -1066,7 +1082,7 @@
         <v>0.6735098963155296</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1195,7 +1211,7 @@
         <v>0.7490832250910372</v>
       </c>
       <c r="L15" t="n">
-        <v>4.29287</v>
+        <v>4.262258</v>
       </c>
       <c r="M15" t="n">
         <v>0.7490832250910372</v>
@@ -1240,13 +1256,13 @@
         <v>0.7282431463850354</v>
       </c>
       <c r="L16" t="n">
-        <v>3.057564</v>
+        <v>3.026952</v>
       </c>
       <c r="M16" t="n">
         <v>0.7282431463850354</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1375,7 +1391,7 @@
         <v>0.8674042443064183</v>
       </c>
       <c r="L19" t="n">
-        <v>4.670111</v>
+        <v>4.650822</v>
       </c>
       <c r="M19" t="n">
         <v>0.8674042443064183</v>
@@ -1420,13 +1436,13 @@
         <v>0.8692675983436853</v>
       </c>
       <c r="L20" t="n">
-        <v>3.305647</v>
+        <v>3.286358</v>
       </c>
       <c r="M20" t="n">
         <v>0.8692675983436853</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1555,7 +1571,7 @@
         <v>0.8429858381471252</v>
       </c>
       <c r="L23" t="n">
-        <v>6.552994000000001</v>
+        <v>6.54002</v>
       </c>
       <c r="M23" t="n">
         <v>0.8429858381471252</v>
@@ -1600,13 +1616,13 @@
         <v>0.8194447743932295</v>
       </c>
       <c r="L24" t="n">
-        <v>3.438041</v>
+        <v>3.425067</v>
       </c>
       <c r="M24" t="n">
         <v>0.8194447743932295</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1735,7 +1751,7 @@
         <v>0.7796945326845552</v>
       </c>
       <c r="L27" t="n">
-        <v>8.464406</v>
+        <v>8.433748000000001</v>
       </c>
       <c r="M27" t="n">
         <v>0.7796945326845552</v>
@@ -1780,13 +1796,13 @@
         <v>0.751691163221671</v>
       </c>
       <c r="L28" t="n">
-        <v>4.475638</v>
+        <v>4.44498</v>
       </c>
       <c r="M28" t="n">
         <v>0.751691163221671</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1915,7 +1931,7 @@
         <v>0.6273182946582756</v>
       </c>
       <c r="L31" t="n">
-        <v>4.810179</v>
+        <v>4.802888</v>
       </c>
       <c r="M31" t="n">
         <v>0.6273182946582756</v>
@@ -1960,13 +1976,13 @@
         <v>0.6056028665007028</v>
       </c>
       <c r="L32" t="n">
-        <v>4.524217</v>
+        <v>4.516926</v>
       </c>
       <c r="M32" t="n">
         <v>0.6056028665007028</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2088,7 +2104,7 @@
         <v>0.6329428463639473</v>
       </c>
       <c r="L35" t="n">
-        <v>19.384634</v>
+        <v>18.712864</v>
       </c>
       <c r="M35" t="n">
         <v>0.6329428463639473</v>
@@ -2133,13 +2149,13 @@
         <v>0.6303397406615706</v>
       </c>
       <c r="L36" t="n">
-        <v>18.590815</v>
+        <v>17.919045</v>
       </c>
       <c r="M36" t="n">
         <v>0.6303397406615706</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2268,7 +2284,7 @@
         <v>0.8386510411666098</v>
       </c>
       <c r="L39" t="n">
-        <v>1.817225</v>
+        <v>1.815374</v>
       </c>
       <c r="M39" t="n">
         <v>0.8386510411666098</v>
@@ -2313,13 +2329,13 @@
         <v>0.785721770308791</v>
       </c>
       <c r="L40" t="n">
-        <v>1.143329</v>
+        <v>1.141478</v>
       </c>
       <c r="M40" t="n">
         <v>0.785721770308791</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2448,7 +2464,7 @@
         <v>0.9792199488491048</v>
       </c>
       <c r="L43" t="n">
-        <v>11.143135</v>
+        <v>11.130273</v>
       </c>
       <c r="M43" t="n">
         <v>0.9792199488491048</v>
@@ -2493,13 +2509,13 @@
         <v>0.9639013213981245</v>
       </c>
       <c r="L44" t="n">
-        <v>6.416089</v>
+        <v>6.403227</v>
       </c>
       <c r="M44" t="n">
         <v>0.9639013213981245</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2628,7 +2644,7 @@
         <v>0.9792553191489362</v>
       </c>
       <c r="L47" t="n">
-        <v>6.643577000000001</v>
+        <v>6.612948</v>
       </c>
       <c r="M47" t="n">
         <v>0.9792553191489362</v>
@@ -2673,13 +2689,13 @@
         <v>0.9665587419056428</v>
       </c>
       <c r="L48" t="n">
-        <v>4.264067</v>
+        <v>4.233438</v>
       </c>
       <c r="M48" t="n">
         <v>0.9665587419056428</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -2808,7 +2824,7 @@
         <v>0.6073623009018826</v>
       </c>
       <c r="L51" t="n">
-        <v>763.9771049999999</v>
+        <v>763.898723</v>
       </c>
       <c r="M51" t="n">
         <v>0.6073623009018826</v>
@@ -2853,13 +2869,13 @@
         <v>0.5580130362124243</v>
       </c>
       <c r="L52" t="n">
-        <v>722.455607</v>
+        <v>722.3772250000001</v>
       </c>
       <c r="M52" t="n">
         <v>0.5580130362124243</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -2988,7 +3004,7 @@
         <v>0.9800667904293642</v>
       </c>
       <c r="L55" t="n">
-        <v>23.721005</v>
+        <v>23.668056</v>
       </c>
       <c r="M55" t="n">
         <v>0.9800667904293642</v>
@@ -3033,13 +3049,13 @@
         <v>0.9743477716752392</v>
       </c>
       <c r="L56" t="n">
-        <v>22.996176</v>
+        <v>22.943227</v>
       </c>
       <c r="M56" t="n">
         <v>0.9743477716752392</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3168,7 +3184,7 @@
         <v>0.9306157325817344</v>
       </c>
       <c r="L59" t="n">
-        <v>5.763612</v>
+        <v>5.734252</v>
       </c>
       <c r="M59" t="n">
         <v>0.9306157325817344</v>
@@ -3213,13 +3229,13 @@
         <v>0.929707848413666</v>
       </c>
       <c r="L60" t="n">
-        <v>4.223911</v>
+        <v>4.194551</v>
       </c>
       <c r="M60" t="n">
         <v>0.929707848413666</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3309,7 +3325,7 @@
         <v>0.8707377454679612</v>
       </c>
       <c r="N62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -3348,7 +3364,7 @@
         <v>0.8932361104123694</v>
       </c>
       <c r="L63" t="n">
-        <v>14.35663</v>
+        <v>14.327472</v>
       </c>
       <c r="M63" t="n">
         <v>0.8932361104123694</v>
@@ -3393,13 +3409,13 @@
         <v>0.8668035501668596</v>
       </c>
       <c r="L64" t="n">
-        <v>9.102905</v>
+        <v>9.073747000000001</v>
       </c>
       <c r="M64" t="n">
         <v>0.8668035501668596</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -3528,7 +3544,7 @@
         <v>0.9751445797957424</v>
       </c>
       <c r="L67" t="n">
-        <v>47.276161</v>
+        <v>47.167211</v>
       </c>
       <c r="M67" t="n">
         <v>0.9751445797957424</v>
@@ -3573,13 +3589,13 @@
         <v>0.9133136458717854</v>
       </c>
       <c r="L68" t="n">
-        <v>25.397662</v>
+        <v>25.288712</v>
       </c>
       <c r="M68" t="n">
         <v>0.9133136458717854</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -3708,7 +3724,7 @@
         <v>0.8754169811433258</v>
       </c>
       <c r="L71" t="n">
-        <v>14.532397</v>
+        <v>14.458542</v>
       </c>
       <c r="M71" t="n">
         <v>0.8754169811433258</v>
@@ -3753,7 +3769,7 @@
         <v>0.8649409812779444</v>
       </c>
       <c r="L72" t="n">
-        <v>14.921531</v>
+        <v>14.847676</v>
       </c>
       <c r="M72" t="n">
         <v>0.8649409812779444</v>
@@ -3824,7 +3840,7 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0.183121</v>
+        <v>0.213435</v>
       </c>
       <c r="M74" t="n">
         <v>0.5450965996276989</v>
@@ -3920,7 +3936,7 @@
         <v>0.6952561460706215</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -4030,7 +4046,7 @@
         <v>0.7127776445109902</v>
       </c>
       <c r="L79" t="n">
-        <v>42.977436</v>
+        <v>44.505579</v>
       </c>
       <c r="M79" t="n">
         <v>0.7127776445109902</v>
@@ -4075,13 +4091,13 @@
         <v>0.720109559102335</v>
       </c>
       <c r="L80" t="n">
-        <v>30.416383</v>
+        <v>31.944526</v>
       </c>
       <c r="M80" t="n">
         <v>0.720109559102335</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -4146,7 +4162,7 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>3.60112</v>
+        <v>4.243838999999999</v>
       </c>
       <c r="M82" t="n">
         <v>0.9178820705894528</v>
@@ -4242,7 +4258,7 @@
         <v>0.9588474098224912</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -4371,7 +4387,7 @@
         <v>0.6197741033070919</v>
       </c>
       <c r="L87" t="n">
-        <v>23.022537</v>
+        <v>22.963749</v>
       </c>
       <c r="M87" t="n">
         <v>0.6197741033070919</v>
@@ -4416,13 +4432,13 @@
         <v>0.608733054709825</v>
       </c>
       <c r="L88" t="n">
-        <v>15.588059</v>
+        <v>15.529271</v>
       </c>
       <c r="M88" t="n">
         <v>0.608733054709825</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -4551,7 +4567,7 @@
         <v>0.8795331790123457</v>
       </c>
       <c r="L91" t="n">
-        <v>5.711414</v>
+        <v>5.666574999999999</v>
       </c>
       <c r="M91" t="n">
         <v>0.8795331790123457</v>
@@ -4596,13 +4612,13 @@
         <v>0.8731192129629629</v>
       </c>
       <c r="L92" t="n">
-        <v>3.476574</v>
+        <v>3.431735</v>
       </c>
       <c r="M92" t="n">
         <v>0.8731192129629629</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -4667,7 +4683,7 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.356684</v>
+        <v>1.659849</v>
       </c>
       <c r="M94" t="n">
         <v>0.3018133168276543</v>
@@ -4763,7 +4779,7 @@
         <v>0.7586691952052512</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
@@ -4892,7 +4908,7 @@
         <v>0.8224644973264432</v>
       </c>
       <c r="L99" t="n">
-        <v>2.347874</v>
+        <v>2.32201</v>
       </c>
       <c r="M99" t="n">
         <v>0.8224644973264432</v>
@@ -4937,13 +4953,13 @@
         <v>0.8315310898077607</v>
       </c>
       <c r="L100" t="n">
-        <v>1.681389</v>
+        <v>1.655525</v>
       </c>
       <c r="M100" t="n">
         <v>0.8315310898077607</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -5072,7 +5088,7 @@
         <v>0.8853482368944174</v>
       </c>
       <c r="L103" t="n">
-        <v>385.573983</v>
+        <v>385.269465</v>
       </c>
       <c r="M103" t="n">
         <v>0.8853482368944174</v>
@@ -5117,13 +5133,13 @@
         <v>0.8682522175583455</v>
       </c>
       <c r="L104" t="n">
-        <v>303.05963</v>
+        <v>302.755112</v>
       </c>
       <c r="M104" t="n">
         <v>0.8682522175583455</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -5252,7 +5268,7 @@
         <v>0.954052197802198</v>
       </c>
       <c r="L107" t="n">
-        <v>21.900289</v>
+        <v>21.868926</v>
       </c>
       <c r="M107" t="n">
         <v>0.954052197802198</v>
@@ -5297,13 +5313,13 @@
         <v>0.8709478021978021</v>
       </c>
       <c r="L108" t="n">
-        <v>12.832568</v>
+        <v>12.801205</v>
       </c>
       <c r="M108" t="n">
         <v>0.8709478021978021</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -5413,7 +5429,7 @@
         <v>0.4373896662388113</v>
       </c>
       <c r="L111" t="n">
-        <v>646.36931</v>
+        <v>646.80098</v>
       </c>
       <c r="M111" t="n">
         <v>0.4373896662388113</v>
@@ -5458,13 +5474,13 @@
         <v>0.493079680171551</v>
       </c>
       <c r="L112" t="n">
-        <v>380.771825</v>
+        <v>381.203495</v>
       </c>
       <c r="M112" t="n">
         <v>0.493079680171551</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
@@ -5593,7 +5609,7 @@
         <v>0.9573697193956214</v>
       </c>
       <c r="L115" t="n">
-        <v>2.214273</v>
+        <v>2.214463</v>
       </c>
       <c r="M115" t="n">
         <v>0.9573697193956214</v>
@@ -5638,13 +5654,13 @@
         <v>0.8956213382670367</v>
       </c>
       <c r="L116" t="n">
-        <v>1.748371</v>
+        <v>1.748561</v>
       </c>
       <c r="M116" t="n">
         <v>0.8956213382670367</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
@@ -5773,7 +5789,7 @@
         <v>0.9454135177521596</v>
       </c>
       <c r="L119" t="n">
-        <v>5.290018</v>
+        <v>5.275169</v>
       </c>
       <c r="M119" t="n">
         <v>0.9454135177521596</v>
@@ -5818,13 +5834,13 @@
         <v>0.9464389102374616</v>
       </c>
       <c r="L120" t="n">
-        <v>3.675263</v>
+        <v>3.660414</v>
       </c>
       <c r="M120" t="n">
         <v>0.9464389102374616</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
@@ -5953,7 +5969,7 @@
         <v>0.9857502927263728</v>
       </c>
       <c r="L123" t="n">
-        <v>5.344968</v>
+        <v>5.339348999999999</v>
       </c>
       <c r="M123" t="n">
         <v>0.9857502927263728</v>
@@ -5998,13 +6014,13 @@
         <v>0.9412180394218286</v>
       </c>
       <c r="L124" t="n">
-        <v>2.58802</v>
+        <v>2.582401</v>
       </c>
       <c r="M124" t="n">
         <v>0.9412180394218286</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125">
@@ -6133,7 +6149,7 @@
         <v>0.8052235787898532</v>
       </c>
       <c r="L127" t="n">
-        <v>2.207931</v>
+        <v>2.150039</v>
       </c>
       <c r="M127" t="n">
         <v>0.8052235787898532</v>
@@ -6178,13 +6194,13 @@
         <v>0.8067169274452534</v>
       </c>
       <c r="L128" t="n">
-        <v>1.899016</v>
+        <v>1.841124</v>
       </c>
       <c r="M128" t="n">
         <v>0.8067169274452534</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
@@ -6313,7 +6329,7 @@
         <v>0.5736597759693398</v>
       </c>
       <c r="L131" t="n">
-        <v>44.034649</v>
+        <v>51.20136600000001</v>
       </c>
       <c r="M131" t="n">
         <v>0.5736597759693398</v>
@@ -6358,13 +6374,13 @@
         <v>0.577069722568228</v>
       </c>
       <c r="L132" t="n">
-        <v>32.486183</v>
+        <v>39.6529</v>
       </c>
       <c r="M132" t="n">
         <v>0.577069722568228</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
@@ -6493,7 +6509,7 @@
         <v>0.9120841819477176</v>
       </c>
       <c r="L135" t="n">
-        <v>1.579808</v>
+        <v>1.577587</v>
       </c>
       <c r="M135" t="n">
         <v>0.9120841819477176</v>
@@ -6538,13 +6554,13 @@
         <v>0.913533099608314</v>
       </c>
       <c r="L136" t="n">
-        <v>1.231664</v>
+        <v>1.229443</v>
       </c>
       <c r="M136" t="n">
         <v>0.913533099608314</v>
       </c>
       <c r="N136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137">
@@ -6673,7 +6689,7 @@
         <v>0.8917078458445366</v>
       </c>
       <c r="L139" t="n">
-        <v>2.632434</v>
+        <v>2.631021</v>
       </c>
       <c r="M139" t="n">
         <v>0.8917078458445366</v>
@@ -6718,13 +6734,13 @@
         <v>0.885266029600562</v>
       </c>
       <c r="L140" t="n">
-        <v>2.005704</v>
+        <v>2.004291</v>
       </c>
       <c r="M140" t="n">
         <v>0.885266029600562</v>
       </c>
       <c r="N140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
@@ -6853,7 +6869,7 @@
         <v>0.8818696555539202</v>
       </c>
       <c r="L143" t="n">
-        <v>6.884664</v>
+        <v>6.886506</v>
       </c>
       <c r="M143" t="n">
         <v>0.8818696555539202</v>
@@ -6898,13 +6914,13 @@
         <v>0.8515590385821631</v>
       </c>
       <c r="L144" t="n">
-        <v>3.553988</v>
+        <v>3.55583</v>
       </c>
       <c r="M144" t="n">
         <v>0.8515590385821631</v>
       </c>
       <c r="N144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145">
@@ -7014,7 +7030,7 @@
         <v>0.6050169406809366</v>
       </c>
       <c r="L147" t="n">
-        <v>755.7428580000001</v>
+        <v>794.8276940000001</v>
       </c>
       <c r="M147" t="n">
         <v>0.6050169406809366</v>
@@ -7059,13 +7075,13 @@
         <v>0.7367952180951104</v>
       </c>
       <c r="L148" t="n">
-        <v>635.0749619999999</v>
+        <v>674.159798</v>
       </c>
       <c r="M148" t="n">
         <v>0.7367952180951104</v>
       </c>
       <c r="N148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149">
@@ -7194,7 +7210,7 @@
         <v>0.6834125588396149</v>
       </c>
       <c r="L151" t="n">
-        <v>28.765052</v>
+        <v>28.753399</v>
       </c>
       <c r="M151" t="n">
         <v>0.6834125588396149</v>
@@ -7239,13 +7255,13 @@
         <v>0.6406182478852309</v>
       </c>
       <c r="L152" t="n">
-        <v>3.554499</v>
+        <v>3.542846</v>
       </c>
       <c r="M152" t="n">
         <v>0.6406182478852309</v>
       </c>
       <c r="N152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
@@ -7374,7 +7390,7 @@
         <v>0.7325544631521609</v>
       </c>
       <c r="L155" t="n">
-        <v>11.281728</v>
+        <v>11.265786</v>
       </c>
       <c r="M155" t="n">
         <v>0.7325544631521609</v>
@@ -7419,13 +7435,13 @@
         <v>0.7255465388740625</v>
       </c>
       <c r="L156" t="n">
-        <v>5.252722</v>
+        <v>5.23678</v>
       </c>
       <c r="M156" t="n">
         <v>0.7255465388740625</v>
       </c>
       <c r="N156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157">
@@ -7547,7 +7563,7 @@
         <v>0.7362523817467309</v>
       </c>
       <c r="L159" t="n">
-        <v>461.745752</v>
+        <v>464.780416</v>
       </c>
       <c r="M159" t="n">
         <v>0.7362523817467309</v>
@@ -7592,13 +7608,13 @@
         <v>0.731595063328388</v>
       </c>
       <c r="L160" t="n">
-        <v>448.666878</v>
+        <v>451.701542</v>
       </c>
       <c r="M160" t="n">
         <v>0.731595063328388</v>
       </c>
       <c r="N160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161">
@@ -7727,7 +7743,7 @@
         <v>0.6847955513140123</v>
       </c>
       <c r="L163" t="n">
-        <v>30.937514</v>
+        <v>30.925671</v>
       </c>
       <c r="M163" t="n">
         <v>0.6847955513140123</v>
@@ -7772,13 +7788,13 @@
         <v>0.6655956310163569</v>
       </c>
       <c r="L164" t="n">
-        <v>26.038254</v>
+        <v>26.026411</v>
       </c>
       <c r="M164" t="n">
         <v>0.6655956310163569</v>
       </c>
       <c r="N164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165">
@@ -7907,7 +7923,7 @@
         <v>0.7882978843652539</v>
       </c>
       <c r="L167" t="n">
-        <v>3.189149</v>
+        <v>3.186363</v>
       </c>
       <c r="M167" t="n">
         <v>0.7882978843652539</v>
@@ -7952,13 +7968,13 @@
         <v>0.7656682802657299</v>
       </c>
       <c r="L168" t="n">
-        <v>2.784966</v>
+        <v>2.78218</v>
       </c>
       <c r="M168" t="n">
         <v>0.7656682802657299</v>
       </c>
       <c r="N168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="169">
@@ -8087,13 +8103,13 @@
         <v>0.4270833333333333</v>
       </c>
       <c r="L171" t="n">
-        <v>1.784591</v>
+        <v>1.780266</v>
       </c>
       <c r="M171" t="n">
         <v>0.4270833333333333</v>
       </c>
       <c r="N171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172">
@@ -8132,7 +8148,7 @@
         <v>0.4217261904761905</v>
       </c>
       <c r="L172" t="n">
-        <v>1.211969</v>
+        <v>1.207644</v>
       </c>
       <c r="M172" t="n">
         <v>0.4217261904761905</v>
@@ -8267,7 +8283,7 @@
         <v>0.9046789868376476</v>
       </c>
       <c r="L175" t="n">
-        <v>74.250244</v>
+        <v>74.32092399999999</v>
       </c>
       <c r="M175" t="n">
         <v>0.9046789868376476</v>
@@ -8312,13 +8328,13 @@
         <v>0.8760835779838435</v>
       </c>
       <c r="L176" t="n">
-        <v>35.936339</v>
+        <v>36.007019</v>
       </c>
       <c r="M176" t="n">
         <v>0.8760835779838435</v>
       </c>
       <c r="N176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="177">
@@ -8428,7 +8444,7 @@
         <v>0.490526972483848</v>
       </c>
       <c r="L179" t="n">
-        <v>520.2596040000001</v>
+        <v>639.615916</v>
       </c>
       <c r="M179" t="n">
         <v>0.490526972483848</v>
@@ -8473,13 +8489,13 @@
         <v>0.5012462475010605</v>
       </c>
       <c r="L180" t="n">
-        <v>367.005612</v>
+        <v>486.361924</v>
       </c>
       <c r="M180" t="n">
         <v>0.5012462475010605</v>
       </c>
       <c r="N180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="181">
@@ -8608,7 +8624,7 @@
         <v>0.5924944469137565</v>
       </c>
       <c r="L183" t="n">
-        <v>4.694137</v>
+        <v>4.668544</v>
       </c>
       <c r="M183" t="n">
         <v>0.5924944469137565</v>
@@ -8653,13 +8669,13 @@
         <v>0.5923823181302825</v>
       </c>
       <c r="L184" t="n">
-        <v>4.268226</v>
+        <v>4.242633</v>
       </c>
       <c r="M184" t="n">
         <v>0.5923823181302825</v>
       </c>
       <c r="N184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="185">
@@ -8769,7 +8785,7 @@
         <v>0.6596943553437395</v>
       </c>
       <c r="L187" t="n">
-        <v>327.257397</v>
+        <v>653.234692</v>
       </c>
       <c r="M187" t="n">
         <v>0.6596943553437395</v>
@@ -8814,13 +8830,13 @@
         <v>0.6578342285278733</v>
       </c>
       <c r="L188" t="n">
-        <v>264.59866</v>
+        <v>590.575955</v>
       </c>
       <c r="M188" t="n">
         <v>0.6578342285278733</v>
       </c>
       <c r="N188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="189">
@@ -8949,7 +8965,7 @@
         <v>0.684631746031746</v>
       </c>
       <c r="L191" t="n">
-        <v>5.197502</v>
+        <v>5.157005</v>
       </c>
       <c r="M191" t="n">
         <v>0.684631746031746</v>
@@ -8994,13 +9010,13 @@
         <v>0.6962793650793651</v>
       </c>
       <c r="L192" t="n">
-        <v>4.608563</v>
+        <v>4.568066</v>
       </c>
       <c r="M192" t="n">
         <v>0.6962793650793651</v>
       </c>
       <c r="N192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="193">
@@ -9129,7 +9145,7 @@
         <v>0.6759954291483063</v>
       </c>
       <c r="L195" t="n">
-        <v>2.9452</v>
+        <v>2.899859</v>
       </c>
       <c r="M195" t="n">
         <v>0.6759954291483063</v>
@@ -9174,13 +9190,13 @@
         <v>0.6586582763913214</v>
       </c>
       <c r="L196" t="n">
-        <v>2.382324</v>
+        <v>2.336983</v>
       </c>
       <c r="M196" t="n">
         <v>0.6586582763913214</v>
       </c>
       <c r="N196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197">
@@ -9255,7 +9271,7 @@
         <v>203.735982</v>
       </c>
       <c r="H198" t="n">
-        <v>48.180683</v>
+        <v>48.18068299999999</v>
       </c>
       <c r="I198" t="n">
         <v>1</v>
@@ -9309,7 +9325,7 @@
         <v>0.7818016747186043</v>
       </c>
       <c r="L199" t="n">
-        <v>11.487736</v>
+        <v>12.310083</v>
       </c>
       <c r="M199" t="n">
         <v>0.7818016747186043</v>
@@ -9354,13 +9370,13 @@
         <v>0.7935149599929394</v>
       </c>
       <c r="L200" t="n">
-        <v>9.283927</v>
+        <v>10.106274</v>
       </c>
       <c r="M200" t="n">
         <v>0.7935149599929394</v>
       </c>
       <c r="N200" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="201">
@@ -9489,7 +9505,7 @@
         <v>0.5515730437325312</v>
       </c>
       <c r="L203" t="n">
-        <v>4.149985</v>
+        <v>4.109387</v>
       </c>
       <c r="M203" t="n">
         <v>0.5515730437325312</v>
@@ -9534,13 +9550,13 @@
         <v>0.5291285828812423</v>
       </c>
       <c r="L204" t="n">
-        <v>3.126091</v>
+        <v>3.085493</v>
       </c>
       <c r="M204" t="n">
         <v>0.5291285828812423</v>
       </c>
       <c r="N204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="205">
@@ -9669,7 +9685,7 @@
         <v>0.8848127798127798</v>
       </c>
       <c r="L207" t="n">
-        <v>1.671654</v>
+        <v>1.666625</v>
       </c>
       <c r="M207" t="n">
         <v>0.8848127798127798</v>
@@ -9714,13 +9730,13 @@
         <v>0.8320634920634921</v>
       </c>
       <c r="L208" t="n">
-        <v>1.3641</v>
+        <v>1.359071</v>
       </c>
       <c r="M208" t="n">
         <v>0.8320634920634921</v>
       </c>
       <c r="N208" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="209">
@@ -9849,7 +9865,7 @@
         <v>0.8037514583877495</v>
       </c>
       <c r="L211" t="n">
-        <v>3.162909</v>
+        <v>3.177856</v>
       </c>
       <c r="M211" t="n">
         <v>0.8037514583877495</v>
@@ -9894,13 +9910,13 @@
         <v>0.7789171298591299</v>
       </c>
       <c r="L212" t="n">
-        <v>2.50133</v>
+        <v>2.516277</v>
       </c>
       <c r="M212" t="n">
         <v>0.7789171298591299</v>
       </c>
       <c r="N212" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="213">
@@ -9939,7 +9955,7 @@
         <v>0.6609110795643359</v>
       </c>
       <c r="L213" t="n">
-        <v>0.2838719999999999</v>
+        <v>0.283872</v>
       </c>
       <c r="M213" t="n">
         <v>0.6609110795643359</v>
@@ -10029,7 +10045,7 @@
         <v>0.4380996465757931</v>
       </c>
       <c r="L215" t="n">
-        <v>3.806215</v>
+        <v>3.797973</v>
       </c>
       <c r="M215" t="n">
         <v>0.4380996465757931</v>
@@ -10074,13 +10090,13 @@
         <v>0.45612267695798</v>
       </c>
       <c r="L216" t="n">
-        <v>3.574157</v>
+        <v>3.565915</v>
       </c>
       <c r="M216" t="n">
         <v>0.45612267695798</v>
       </c>
       <c r="N216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217">
@@ -10224,13 +10240,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4007.726803</v>
+        <v>4733.146036</v>
       </c>
       <c r="C3" t="n">
         <v>0.7558331557550066</v>
       </c>
       <c r="D3" t="n">
-        <v>3.602898109068408</v>
+        <v>3.675149904351901</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
@@ -10253,13 +10269,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4994.72635</v>
+        <v>5720.145583</v>
       </c>
       <c r="C4" t="n">
         <v>0.7673830533298976</v>
       </c>
       <c r="D4" t="n">
-        <v>3.698511699180513</v>
+        <v>3.757407082130257</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
@@ -10282,13 +10298,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2594514.797863</v>
+        <v>2594516.070236</v>
       </c>
       <c r="C5" t="n">
         <v>0.6829860537773095</v>
       </c>
       <c r="D5" t="n">
-        <v>6.414056152044597</v>
+        <v>6.414056365026399</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -10309,7 +10325,7 @@
         <v>1203.747371709796</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3081614187368837</v>
+        <v>0.3530817044276489</v>
       </c>
       <c r="D6" t="n">
         <v>3.080535351884883</v>
@@ -10325,13 +10341,13 @@
     </row>
     <row r="7">
       <c r="B7" t="n">
-        <v>4613772.244081069</v>
+        <v>4613774.506715775</v>
       </c>
       <c r="C7" t="n">
-        <v>1.125613872235522</v>
+        <v>1.175511588860741</v>
       </c>
       <c r="D7" t="n">
-        <v>6.664056152044597</v>
+        <v>6.664056365026399</v>
       </c>
       <c r="E7" t="b">
         <v>1</v>
@@ -10557,7 +10573,7 @@
         <v>0.5886528972883893</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -10737,7 +10753,7 @@
         <v>0.7573497934312421</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -10898,7 +10914,7 @@
         <v>0.6735159489471086</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -11078,7 +11094,7 @@
         <v>0.7282431463850354</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -11258,7 +11274,7 @@
         <v>0.8692675983436853</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -11438,7 +11454,7 @@
         <v>0.8187117309531994</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -11477,7 +11493,7 @@
         <v>0.3040209184306812</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2037969999999999</v>
+        <v>0.203797</v>
       </c>
       <c r="M25" t="n">
         <v>0.3040209184306812</v>
@@ -11618,7 +11634,7 @@
         <v>0.7540465958632078</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -11798,7 +11814,7 @@
         <v>0.6056028665007028</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -11971,7 +11987,7 @@
         <v>0.6303397406615706</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -12151,7 +12167,7 @@
         <v>0.785721770308791</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -12280,7 +12296,7 @@
         <v>0.981544384057971</v>
       </c>
       <c r="L43" t="n">
-        <v>9.439984000000001</v>
+        <v>9.439983999999999</v>
       </c>
       <c r="M43" t="n">
         <v>0.981544384057971</v>
@@ -12331,7 +12347,7 @@
         <v>0.9586163949275364</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -12511,7 +12527,7 @@
         <v>0.96709065679926</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -12691,7 +12707,7 @@
         <v>0.5579818597418351</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -12871,7 +12887,7 @@
         <v>0.9743477716752392</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -13051,7 +13067,7 @@
         <v>0.9299717373025548</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -13231,7 +13247,7 @@
         <v>0.8670760594321746</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -13575,7 +13591,7 @@
         <v>0.8649409812779444</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -13640,7 +13656,7 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0.1885379999999999</v>
+        <v>0.188538</v>
       </c>
       <c r="M74" t="n">
         <v>0.543796483343729</v>
@@ -13736,7 +13752,7 @@
         <v>0.6952561460706215</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -13916,7 +13932,7 @@
         <v>0.6931694746178979</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -14077,7 +14093,7 @@
         <v>0.95865414273146</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -14257,7 +14273,7 @@
         <v>0.6087236019670861</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -14437,7 +14453,7 @@
         <v>0.8776041666666666</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -14598,7 +14614,7 @@
         <v>0.7586691952052512</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
@@ -14778,7 +14794,7 @@
         <v>0.8315310898077607</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -14958,7 +14974,7 @@
         <v>0.8682405508916787</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -15138,7 +15154,7 @@
         <v>0.8709478021978021</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -15299,7 +15315,7 @@
         <v>0.4927930135048844</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
@@ -15479,7 +15495,7 @@
         <v>0.9062596361393772</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
@@ -15659,7 +15675,7 @@
         <v>0.9477722435707951</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
@@ -15839,7 +15855,7 @@
         <v>0.9412180394218286</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125">
@@ -16019,7 +16035,7 @@
         <v>0.8067169274452534</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
@@ -16367,7 +16383,7 @@
         <v>0.913533099608314</v>
       </c>
       <c r="N136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137">
@@ -16451,7 +16467,7 @@
         <v>0.8704884577186736</v>
       </c>
       <c r="L138" t="n">
-        <v>99.24345700000001</v>
+        <v>99.24345699999999</v>
       </c>
       <c r="M138" t="n">
         <v>0.8704884577186736</v>
@@ -16547,7 +16563,7 @@
         <v>0.882768028001841</v>
       </c>
       <c r="N140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
@@ -16727,7 +16743,7 @@
         <v>0.851662441597493</v>
       </c>
       <c r="N144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145">
@@ -16888,7 +16904,7 @@
         <v>0.7383355065121452</v>
       </c>
       <c r="N148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149">
@@ -17068,7 +17084,7 @@
         <v>0.6406182478852309</v>
       </c>
       <c r="N152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
@@ -17248,7 +17264,7 @@
         <v>0.7255465388740625</v>
       </c>
       <c r="N156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157">
@@ -17377,7 +17393,7 @@
         <v>0.734452566524874</v>
       </c>
       <c r="L159" t="n">
-        <v>472.019114</v>
+        <v>472.0191139999999</v>
       </c>
       <c r="M159" t="n">
         <v>0.734452566524874</v>
@@ -17428,7 +17444,7 @@
         <v>0.730440343292586</v>
       </c>
       <c r="N160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161">
@@ -17608,7 +17624,7 @@
         <v>0.6653236310163568</v>
       </c>
       <c r="N164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165">
@@ -17788,7 +17804,7 @@
         <v>0.7656682802657299</v>
       </c>
       <c r="N168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="169">
@@ -17923,7 +17939,7 @@
         <v>0.4446428571428572</v>
       </c>
       <c r="N171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172">
@@ -18148,7 +18164,7 @@
         <v>0.8738343484381629</v>
       </c>
       <c r="N176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="177">
@@ -18471,7 +18487,7 @@
         <v>0.5950278115750811</v>
       </c>
       <c r="N184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="185">
@@ -18632,7 +18648,7 @@
         <v>0.6597562731423303</v>
       </c>
       <c r="N188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="189">
@@ -18812,7 +18828,7 @@
         <v>0.6962793650793651</v>
       </c>
       <c r="N192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="193">
@@ -18992,7 +19008,7 @@
         <v>0.6586582763913214</v>
       </c>
       <c r="N196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197">
@@ -19031,7 +19047,7 @@
         <v>0.5051604712368089</v>
       </c>
       <c r="L197" t="n">
-        <v>0.3674179999999999</v>
+        <v>0.367418</v>
       </c>
       <c r="M197" t="n">
         <v>0.5051604712368089</v>
@@ -19172,7 +19188,7 @@
         <v>0.789807379097932</v>
       </c>
       <c r="N200" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="201">
@@ -19352,7 +19368,7 @@
         <v>0.529359628641782</v>
       </c>
       <c r="N204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="205">
@@ -19391,7 +19407,7 @@
         <v>0.2496920215624142</v>
       </c>
       <c r="L205" t="n">
-        <v>0.313471</v>
+        <v>0.3134710000000001</v>
       </c>
       <c r="M205" t="n">
         <v>0.2496920215624142</v>
@@ -19532,7 +19548,7 @@
         <v>0.8320634920634921</v>
       </c>
       <c r="N208" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="209">
@@ -19712,7 +19728,7 @@
         <v>0.77891712985913</v>
       </c>
       <c r="N212" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="213">
@@ -19892,7 +19908,7 @@
         <v>0.45612267695798</v>
       </c>
       <c r="N216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217">
@@ -20167,6 +20183,22 @@
   </sheetPr>
   <dimension ref="A1:N29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="5" customWidth="1" min="14" max="14"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -20372,7 +20404,7 @@
         <v>0.8019571697394763</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -20432,7 +20464,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0.377413</v>
+        <v>0.202329</v>
       </c>
       <c r="L6" t="n">
         <v>0.6519011505541282</v>
@@ -20533,7 +20565,7 @@
         <v>0.7856214385538499</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -20713,7 +20745,7 @@
         <v>0.8822896289727504</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -20773,7 +20805,7 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>345600</v>
+        <v>345608.854457</v>
       </c>
       <c r="L14" t="n">
         <v>0.4071121623416927</v>
@@ -20874,7 +20906,7 @@
         <v>0.7802321768929626</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -21054,7 +21086,7 @@
         <v>0.7047619827845791</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -21234,7 +21266,7 @@
         <v>0.8284211944045828</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -21414,7 +21446,7 @@
         <v>0.5683028838386387</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
